--- a/src/main/webapp/content/files/oncologyTherapies/fda_approved_oncology_therapies.xlsx
+++ b/src/main/webapp/content/files/oncologyTherapies/fda_approved_oncology_therapies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luc2\Desktop\oncokb\oncokb-public\src\main\webapp\content\files\oncologyTherapies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luc2/Documents/oncokb/oncokb-public/src/main/webapp/content/files/oncologyTherapies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45EF53A-463B-45D4-BCE1-BA0BB0E9A6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3598799-5264-8C48-B722-891F8EC70695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4716" yWindow="576" windowWidth="21480" windowHeight="15456" xr2:uid="{D862B214-800F-AF40-9BAA-60FE1781D5C8}"/>
+    <workbookView xWindow="10600" yWindow="1480" windowWidth="33820" windowHeight="23700" xr2:uid="{D862B214-800F-AF40-9BAA-60FE1781D5C8}"/>
   </bookViews>
   <sheets>
     <sheet name="FDA-Approved Oncology Therapies" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="495">
   <si>
     <t>Year of drug’s first FDA- approval</t>
   </si>
@@ -1722,6 +1722,27 @@
   </si>
   <si>
     <t>Telomerase template antagonist</t>
+  </si>
+  <si>
+    <t>Afamitresgene autoleucel</t>
+  </si>
+  <si>
+    <t>HLA-A*02:01P, -A*02:02P, -A*02:03P, or -A*02:06P positive and MAGE-A4 antigen positive</t>
+  </si>
+  <si>
+    <t>T cell receptor (TCR) therapy</t>
+  </si>
+  <si>
+    <t>MAGE-A4-directed TCR therapy</t>
+  </si>
+  <si>
+    <t>Vorasidenib</t>
+  </si>
+  <si>
+    <t>IDH1 R132H/C/G/S/L, IDH2 R172K/M/W/S/G</t>
+  </si>
+  <si>
+    <t>IDH1/IDH2 inhibitor</t>
   </si>
 </sst>
 </file>
@@ -2148,17 +2169,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B89377A-76F6-CA40-8081-AAD80BFAB6B8}">
-  <dimension ref="A1:H223"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H225"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
-    <col min="2" max="2" width="22.19921875" customWidth="1"/>
-    <col min="3" max="3" width="26.19921875" customWidth="1"/>
-    <col min="4" max="4" width="25.796875" customWidth="1"/>
-    <col min="5" max="5" width="27.296875" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2184,7 +2205,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2207,7 +2228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -2230,7 +2251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2256,7 +2277,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2279,7 +2300,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -2302,7 +2323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -2328,7 +2349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -2351,7 +2372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -2377,7 +2398,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -2403,7 +2424,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" s="2" customFormat="1" ht="70" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -2429,7 +2450,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -2452,7 +2473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
@@ -2475,7 +2496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
@@ -2501,7 +2522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
@@ -2524,7 +2545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
@@ -2547,7 +2568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
         <v>2002</v>
       </c>
@@ -2573,7 +2594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
         <v>2002</v>
       </c>
@@ -2596,7 +2617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
         <v>2002</v>
       </c>
@@ -2619,7 +2640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
         <v>2003</v>
       </c>
@@ -2643,7 +2664,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
         <v>2003</v>
       </c>
@@ -2666,7 +2687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
         <v>2003</v>
       </c>
@@ -2692,7 +2713,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
         <v>2003</v>
       </c>
@@ -2718,7 +2739,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="2">
         <v>2004</v>
       </c>
@@ -2741,7 +2762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="2">
         <v>2004</v>
       </c>
@@ -2764,7 +2785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="2" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
         <v>2004</v>
       </c>
@@ -2790,7 +2811,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
         <v>2004</v>
       </c>
@@ -2813,7 +2834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="2">
         <v>2004</v>
       </c>
@@ -2839,7 +2860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A29" s="2">
         <v>2004</v>
       </c>
@@ -2863,7 +2884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="2">
         <v>2005</v>
       </c>
@@ -2886,7 +2907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="2">
         <v>2005</v>
       </c>
@@ -2909,7 +2930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A32" s="2">
         <v>2006</v>
       </c>
@@ -2935,7 +2956,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
         <v>2006</v>
       </c>
@@ -2958,7 +2979,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A34" s="2">
         <v>2006</v>
       </c>
@@ -2981,7 +3002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="2" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A35" s="2">
         <v>2006</v>
       </c>
@@ -3007,7 +3028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="2">
         <v>2006</v>
       </c>
@@ -3033,7 +3054,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="2">
         <v>2006</v>
       </c>
@@ -3056,7 +3077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
         <v>2007</v>
       </c>
@@ -3080,7 +3101,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
         <v>2007</v>
       </c>
@@ -3106,7 +3127,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A40" s="2">
         <v>2007</v>
       </c>
@@ -3132,7 +3153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A41" s="2">
         <v>2007</v>
       </c>
@@ -3156,7 +3177,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A42" s="2">
         <v>2008</v>
       </c>
@@ -3179,7 +3200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A43" s="2">
         <v>2008</v>
       </c>
@@ -3202,7 +3223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A44" s="2">
         <v>2009</v>
       </c>
@@ -3228,7 +3249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A45" s="2">
         <v>2009</v>
       </c>
@@ -3251,7 +3272,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="2">
         <v>2009</v>
       </c>
@@ -3274,7 +3295,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A47" s="2">
         <v>2009</v>
       </c>
@@ -3298,7 +3319,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="2">
         <v>2009</v>
       </c>
@@ -3321,7 +3342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="2">
         <v>2010</v>
       </c>
@@ -3344,7 +3365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A50" s="2">
         <v>2010</v>
       </c>
@@ -3368,7 +3389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A51" s="2">
         <v>2010</v>
       </c>
@@ -3391,7 +3412,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
         <v>2011</v>
       </c>
@@ -3414,7 +3435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
         <v>2011</v>
       </c>
@@ -3438,7 +3459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="2">
         <v>2011</v>
       </c>
@@ -3464,7 +3485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="2">
         <v>2011</v>
       </c>
@@ -3490,7 +3511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="2">
         <v>2011</v>
       </c>
@@ -3514,7 +3535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A57" s="2">
         <v>2011</v>
       </c>
@@ -3537,7 +3558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A58" s="2">
         <v>2011</v>
       </c>
@@ -3560,7 +3581,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A59" s="2">
         <v>2011</v>
       </c>
@@ -3584,7 +3605,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A60" s="2">
         <v>2011</v>
       </c>
@@ -3610,7 +3631,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A61" s="2">
         <v>2012</v>
       </c>
@@ -3633,7 +3654,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A62" s="2">
         <v>2012</v>
       </c>
@@ -3657,7 +3678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A63" s="2">
         <v>2012</v>
       </c>
@@ -3683,7 +3704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A64" s="2">
         <v>2012</v>
       </c>
@@ -3706,7 +3727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A65" s="2">
         <v>2012</v>
       </c>
@@ -3730,7 +3751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="2">
         <v>2012</v>
       </c>
@@ -3753,7 +3774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="2">
         <v>2012</v>
       </c>
@@ -3776,7 +3797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A68" s="2">
         <v>2012</v>
       </c>
@@ -3802,7 +3823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A69" s="2">
         <v>2012</v>
       </c>
@@ -3828,7 +3849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A70" s="2">
         <v>2012</v>
       </c>
@@ -3854,7 +3875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A71" s="2">
         <v>2012</v>
       </c>
@@ -3878,7 +3899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="2">
         <v>2013</v>
       </c>
@@ -3904,7 +3925,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A73" s="2">
         <v>2013</v>
       </c>
@@ -3930,7 +3951,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A74" s="2">
         <v>2013</v>
       </c>
@@ -3956,7 +3977,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A75" s="2">
         <v>2013</v>
       </c>
@@ -3982,7 +4003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A76" s="2">
         <v>2013</v>
       </c>
@@ -4005,7 +4026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A77" s="2">
         <v>2013</v>
       </c>
@@ -4029,7 +4050,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A78" s="2">
         <v>2013</v>
       </c>
@@ -4052,7 +4073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A79" s="2">
         <v>2013</v>
       </c>
@@ -4078,7 +4099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A80" s="2">
         <v>2014</v>
       </c>
@@ -4102,7 +4123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A81" s="2">
         <v>2014</v>
       </c>
@@ -4128,7 +4149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A82" s="2">
         <v>2014</v>
       </c>
@@ -4154,7 +4175,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A83" s="2">
         <v>2014</v>
       </c>
@@ -4180,7 +4201,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A84" s="2">
         <v>2014</v>
       </c>
@@ -4203,7 +4224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A85" s="2">
         <v>2014</v>
       </c>
@@ -4226,7 +4247,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A86" s="2">
         <v>2014</v>
       </c>
@@ -4250,7 +4271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A87" s="2">
         <v>2014</v>
       </c>
@@ -4276,7 +4297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A88" s="2">
         <v>2014</v>
       </c>
@@ -4302,7 +4323,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:8" s="2" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" s="2" customFormat="1" ht="56" x14ac:dyDescent="0.15">
       <c r="A89" s="2">
         <v>2014</v>
       </c>
@@ -4328,7 +4349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A90" s="2">
         <v>2014</v>
       </c>
@@ -4351,7 +4372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A91" s="2">
         <v>2014</v>
       </c>
@@ -4374,7 +4395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A92" s="2">
         <v>2015</v>
       </c>
@@ -4400,7 +4421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A93" s="2">
         <v>2015</v>
       </c>
@@ -4426,7 +4447,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A94" s="2">
         <v>2015</v>
       </c>
@@ -4449,7 +4470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A95" s="2">
         <v>2015</v>
       </c>
@@ -4473,7 +4494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A96" s="2">
         <v>2015</v>
       </c>
@@ -4496,7 +4517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A97" s="2">
         <v>2015</v>
       </c>
@@ -4522,7 +4543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A98" s="2">
         <v>2015</v>
       </c>
@@ -4546,7 +4567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A99" s="2">
         <v>2015</v>
       </c>
@@ -4569,7 +4590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A100" s="2">
         <v>2015</v>
       </c>
@@ -4592,7 +4613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:8" s="2" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A101" s="2">
         <v>2015</v>
       </c>
@@ -4618,7 +4639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A102" s="2">
         <v>2015</v>
       </c>
@@ -4644,7 +4665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A103" s="2">
         <v>2015</v>
       </c>
@@ -4667,7 +4688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A104" s="2">
         <v>2015</v>
       </c>
@@ -4691,7 +4712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A105" s="2">
         <v>2015</v>
       </c>
@@ -4714,7 +4735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A106" s="2">
         <v>2015</v>
       </c>
@@ -4737,7 +4758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A107" s="2">
         <v>2015</v>
       </c>
@@ -4761,7 +4782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A108" s="2">
         <v>2016</v>
       </c>
@@ -4787,7 +4808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A109" s="2">
         <v>2016</v>
       </c>
@@ -4810,7 +4831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:8" s="2" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A110" s="2">
         <v>2016</v>
       </c>
@@ -4836,7 +4857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A111" s="2">
         <v>2016</v>
       </c>
@@ -4859,7 +4880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A112" s="2">
         <v>2017</v>
       </c>
@@ -4885,7 +4906,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A113" s="2">
         <v>2017</v>
       </c>
@@ -4909,7 +4930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A114" s="2">
         <v>2017</v>
       </c>
@@ -4932,7 +4953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A115" s="2">
         <v>2017</v>
       </c>
@@ -4955,7 +4976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A116" s="2">
         <v>2017</v>
       </c>
@@ -4981,7 +5002,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A117" s="2">
         <v>2017</v>
       </c>
@@ -5004,7 +5025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A118" s="2">
         <v>2017</v>
       </c>
@@ -5027,7 +5048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A119" s="2">
         <v>2017</v>
       </c>
@@ -5051,7 +5072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A120" s="2">
         <v>2017</v>
       </c>
@@ -5077,7 +5098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A121" s="2">
         <v>2017</v>
       </c>
@@ -5103,7 +5124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:8" s="2" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A122" s="2">
         <v>2017</v>
       </c>
@@ -5129,7 +5150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A123" s="2">
         <v>2017</v>
       </c>
@@ -5155,7 +5176,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A124" s="2">
         <v>2017</v>
       </c>
@@ -5181,7 +5202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A125" s="2">
         <v>2017</v>
       </c>
@@ -5207,7 +5228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A126" s="2">
         <v>2017</v>
       </c>
@@ -5230,7 +5251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A127" s="2">
         <v>2018</v>
       </c>
@@ -5253,7 +5274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A128" s="2">
         <v>2018</v>
       </c>
@@ -5279,7 +5300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A129" s="2">
         <v>2018</v>
       </c>
@@ -5302,7 +5323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A130" s="2">
         <v>2018</v>
       </c>
@@ -5328,7 +5349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A131" s="2">
         <v>2018</v>
       </c>
@@ -5354,7 +5375,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A132" s="2">
         <v>2018</v>
       </c>
@@ -5377,7 +5398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A133" s="2">
         <v>2018</v>
       </c>
@@ -5403,7 +5424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A134" s="2">
         <v>2018</v>
       </c>
@@ -5427,7 +5448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A135" s="2">
         <v>2018</v>
       </c>
@@ -5450,7 +5471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A136" s="2">
         <v>2018</v>
       </c>
@@ -5476,7 +5497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A137" s="2">
         <v>2018</v>
       </c>
@@ -5502,7 +5523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A138" s="2">
         <v>2018</v>
       </c>
@@ -5528,7 +5549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A139" s="2">
         <v>2018</v>
       </c>
@@ -5554,7 +5575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A140" s="2">
         <v>2018</v>
       </c>
@@ -5578,7 +5599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A141" s="2">
         <v>2018</v>
       </c>
@@ -5601,7 +5622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A142" s="2">
         <v>2018</v>
       </c>
@@ -5624,7 +5645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:8" s="2" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" s="2" customFormat="1" ht="98" x14ac:dyDescent="0.15">
       <c r="A143" s="2">
         <v>2018</v>
       </c>
@@ -5650,7 +5671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A144" s="2">
         <v>2019</v>
       </c>
@@ -5676,7 +5697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A145" s="2">
         <v>2019</v>
       </c>
@@ -5699,7 +5720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A146" s="2">
         <v>2019</v>
       </c>
@@ -5723,7 +5744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A147" s="2">
         <v>2019</v>
       </c>
@@ -5749,7 +5770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A148" s="2">
         <v>2019</v>
       </c>
@@ -5775,7 +5796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A149" s="2">
         <v>2019</v>
       </c>
@@ -5799,7 +5820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A150" s="2">
         <v>2019</v>
       </c>
@@ -5822,7 +5843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A151" s="2">
         <v>2019</v>
       </c>
@@ -5845,7 +5866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A152" s="2">
         <v>2019</v>
       </c>
@@ -5869,7 +5890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A153" s="2">
         <v>2019</v>
       </c>
@@ -5895,7 +5916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A154" s="2">
         <v>2019</v>
       </c>
@@ -5918,7 +5939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A155" s="2">
         <v>2020</v>
       </c>
@@ -5944,7 +5965,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A156" s="2">
         <v>2020</v>
       </c>
@@ -5970,7 +5991,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A157" s="2">
         <v>2020</v>
       </c>
@@ -5993,7 +6014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A158" s="2">
         <v>2020</v>
       </c>
@@ -6017,7 +6038,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A159" s="2">
         <v>2020</v>
       </c>
@@ -6043,7 +6064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A160" s="2">
         <v>2020</v>
       </c>
@@ -6066,7 +6087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A161" s="2">
         <v>2020</v>
       </c>
@@ -6092,7 +6113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A162" s="2">
         <v>2020</v>
       </c>
@@ -6115,7 +6136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A163" s="2">
         <v>2020</v>
       </c>
@@ -6138,7 +6159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A164" s="2">
         <v>2020</v>
       </c>
@@ -6164,7 +6185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A165" s="2">
         <v>2020</v>
       </c>
@@ -6184,7 +6205,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:8" s="2" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A166" s="2">
         <v>2020</v>
       </c>
@@ -6210,7 +6231,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:8" s="2" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A167" s="2">
         <v>2020</v>
       </c>
@@ -6236,7 +6257,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A168" s="2">
         <v>2020</v>
       </c>
@@ -6259,7 +6280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A169" s="2">
         <v>2020</v>
       </c>
@@ -6285,7 +6306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A170" s="2">
         <v>2020</v>
       </c>
@@ -6311,7 +6332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A171" s="2">
         <v>2020</v>
       </c>
@@ -6337,7 +6358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A172" s="2">
         <v>2020</v>
       </c>
@@ -6363,7 +6384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="173" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A173" s="2">
         <v>2020</v>
       </c>
@@ -6387,7 +6408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A174" s="2">
         <v>2020</v>
       </c>
@@ -6413,7 +6434,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A175" s="2">
         <v>2020</v>
       </c>
@@ -6439,7 +6460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A176" s="2">
         <v>2021</v>
       </c>
@@ -6465,7 +6486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A177" s="2">
         <v>2021</v>
       </c>
@@ -6491,7 +6512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A178" s="2">
         <v>2021</v>
       </c>
@@ -6517,7 +6538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:8" s="2" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A179" s="2">
         <v>2021</v>
       </c>
@@ -6543,7 +6564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A180" s="2">
         <v>2021</v>
       </c>
@@ -6566,7 +6587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A181" s="2">
         <v>2021</v>
       </c>
@@ -6592,7 +6613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A182" s="2">
         <v>2021</v>
       </c>
@@ -6616,7 +6637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A183" s="2">
         <v>2021</v>
       </c>
@@ -6639,7 +6660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A184" s="2">
         <v>2021</v>
       </c>
@@ -6662,7 +6683,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A185" s="2">
         <v>2021</v>
       </c>
@@ -6688,7 +6709,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="186" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A186" s="2">
         <v>2021</v>
       </c>
@@ -6711,7 +6732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A187" s="2">
         <v>2021</v>
       </c>
@@ -6737,7 +6758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A188" s="2">
         <v>2021</v>
       </c>
@@ -6763,7 +6784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="189" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A189" s="2">
         <v>2021</v>
       </c>
@@ -6786,7 +6807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A190" s="2">
         <v>2021</v>
       </c>
@@ -6809,7 +6830,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A191" s="2">
         <v>2021</v>
       </c>
@@ -6835,7 +6856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A192" s="2">
         <v>2021</v>
       </c>
@@ -6858,7 +6879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A193" s="2">
         <v>2022</v>
       </c>
@@ -6884,7 +6905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A194" s="2">
         <v>2022</v>
       </c>
@@ -6908,7 +6929,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A195" s="2">
         <v>2022</v>
       </c>
@@ -6934,7 +6955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A196" s="2">
         <v>2022</v>
       </c>
@@ -6960,7 +6981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A197" s="2">
         <v>2022</v>
       </c>
@@ -6984,7 +7005,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A198" s="2">
         <v>2022</v>
       </c>
@@ -7007,7 +7028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A199" s="2">
         <v>2022</v>
       </c>
@@ -7030,7 +7051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A200" s="2">
         <v>2022</v>
       </c>
@@ -7056,7 +7077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A201" s="2">
         <v>2022</v>
       </c>
@@ -7082,7 +7103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A202" s="2">
         <v>2022</v>
       </c>
@@ -7108,7 +7129,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A203" s="2">
         <v>2022</v>
       </c>
@@ -7132,7 +7153,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="204" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A204" s="2">
         <v>2022</v>
       </c>
@@ -7155,7 +7176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A205" s="2">
         <v>2023</v>
       </c>
@@ -7181,7 +7202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:8" s="2" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" s="2" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A206" s="2">
         <v>2023</v>
       </c>
@@ -7207,7 +7228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A207" s="2">
         <v>2023</v>
       </c>
@@ -7230,7 +7251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A208" s="2">
         <v>2023</v>
       </c>
@@ -7253,7 +7274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="209" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A209" s="2">
         <v>2023</v>
       </c>
@@ -7277,7 +7298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="210" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A210" s="2">
         <v>2023</v>
       </c>
@@ -7300,7 +7321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A211" s="2">
         <v>2023</v>
       </c>
@@ -7323,7 +7344,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A212" s="2">
         <v>2023</v>
       </c>
@@ -7347,7 +7368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A213" s="2">
         <v>2023</v>
       </c>
@@ -7373,7 +7394,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A214" s="2">
         <v>2023</v>
       </c>
@@ -7399,7 +7420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A215" s="2">
         <v>2023</v>
       </c>
@@ -7423,7 +7444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A216" s="2">
         <v>2023</v>
       </c>
@@ -7446,7 +7467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="217" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A217" s="2">
         <v>2023</v>
       </c>
@@ -7469,7 +7490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" spans="1:8" s="2" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A218" s="2">
         <v>2023</v>
       </c>
@@ -7492,7 +7513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>2024</v>
       </c>
@@ -7516,7 +7537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="5">
         <v>2024</v>
       </c>
@@ -7540,7 +7561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>2024</v>
       </c>
@@ -7566,7 +7587,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="5">
         <v>2024</v>
       </c>
@@ -7590,7 +7611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="5">
         <v>2024</v>
       </c>
@@ -7612,6 +7633,58 @@
       </c>
       <c r="H223" s="5" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A224" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A225" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7626,42 +7699,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AB9D94-D219-C745-BD3C-1D6167799F61}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="153.19921875" customWidth="1"/>
+    <col min="1" max="1" width="153.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="59" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="42.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>468</v>
       </c>

--- a/src/main/webapp/content/files/oncologyTherapies/fda_approved_oncology_therapies.xlsx
+++ b/src/main/webapp/content/files/oncologyTherapies/fda_approved_oncology_therapies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cavendk1/Documents/New onc therapies/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luc2/MSK/oncokb/oncokb-pipeline/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A50A02A-F303-074A-9252-DA2B75C15630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BF5860-F7FE-8141-A26A-832D3806CA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="760" windowWidth="29020" windowHeight="17440" xr2:uid="{D862B214-800F-AF40-9BAA-60FE1781D5C8}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{D862B214-800F-AF40-9BAA-60FE1781D5C8}"/>
   </bookViews>
   <sheets>
     <sheet name="FDA-Approved Oncology Therapies" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="551">
   <si>
     <t>Year of drug’s first FDA- approval</t>
   </si>
@@ -1895,6 +1895,15 @@
   </si>
   <si>
     <t>Sevabertinib</t>
+  </si>
+  <si>
+    <t>Trastuzumab deruxtecan + Pertuzumab</t>
+  </si>
+  <si>
+    <t>Antibody drug conjugate and monocolonal antibody</t>
+  </si>
+  <si>
+    <t>HER2 (ERBB2)-directed antibody and topoisomerase inhibitor conjugate + anti-HER2 (ERBB2) antibody</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2044,13 +2053,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2365,7 +2371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B89377A-76F6-CA40-8081-AAD80BFAB6B8}">
-  <dimension ref="A1:I250"/>
+  <dimension ref="A1:I251"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" customWidth="1"/>
@@ -2403,7 +2409,7 @@
       </c>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2505,7 +2511,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
@@ -2530,7 +2536,7 @@
       </c>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -2609,7 +2615,7 @@
       </c>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -2636,7 +2642,7 @@
       </c>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A11" s="7">
         <v>2018</v>
       </c>
@@ -2817,7 +2823,7 @@
       </c>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A18" s="7">
         <v>2002</v>
       </c>
@@ -2892,7 +2898,7 @@
       </c>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A21" s="7">
         <v>2003</v>
       </c>
@@ -2917,7 +2923,7 @@
       </c>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A22" s="7">
         <v>2003</v>
       </c>
@@ -2944,7 +2950,7 @@
       </c>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A23" s="7">
         <v>2003</v>
       </c>
@@ -2971,7 +2977,7 @@
       </c>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A24" s="7">
         <v>2004</v>
       </c>
@@ -3048,7 +3054,7 @@
       </c>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A27" s="7">
         <v>2004</v>
       </c>
@@ -3073,7 +3079,7 @@
       </c>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A28" s="7">
         <v>2004</v>
       </c>
@@ -3125,7 +3131,7 @@
       </c>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A30" s="7">
         <v>2005</v>
       </c>
@@ -3177,7 +3183,7 @@
       </c>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A32" s="7">
         <v>2019</v>
       </c>
@@ -3202,7 +3208,7 @@
       </c>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A33" s="7">
         <v>2006</v>
       </c>
@@ -3512,7 +3518,7 @@
       </c>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A45" s="7">
         <v>2009</v>
       </c>
@@ -3537,7 +3543,7 @@
       </c>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A46" s="7">
         <v>2019</v>
       </c>
@@ -3737,7 +3743,7 @@
       </c>
       <c r="I53" s="7"/>
     </row>
-    <row r="54" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A54" s="7">
         <v>2011</v>
       </c>
@@ -3764,7 +3770,7 @@
       </c>
       <c r="I54" s="7"/>
     </row>
-    <row r="55" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A55" s="7">
         <v>2020</v>
       </c>
@@ -3791,7 +3797,7 @@
       </c>
       <c r="I55" s="7"/>
     </row>
-    <row r="56" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A56" s="7">
         <v>2011</v>
       </c>
@@ -3816,7 +3822,7 @@
       </c>
       <c r="I56" s="7"/>
     </row>
-    <row r="57" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A57" s="7">
         <v>2011</v>
       </c>
@@ -3841,7 +3847,7 @@
       </c>
       <c r="I57" s="7"/>
     </row>
-    <row r="58" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A58" s="7">
         <v>2011</v>
       </c>
@@ -3893,7 +3899,7 @@
       </c>
       <c r="I59" s="7"/>
     </row>
-    <row r="60" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A60" s="7">
         <v>2011</v>
       </c>
@@ -3970,7 +3976,7 @@
       </c>
       <c r="I62" s="7"/>
     </row>
-    <row r="63" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A63" s="7">
         <v>2021</v>
       </c>
@@ -4022,7 +4028,7 @@
       </c>
       <c r="I64" s="7"/>
     </row>
-    <row r="65" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A65" s="7">
         <v>2012</v>
       </c>
@@ -4072,7 +4078,7 @@
       </c>
       <c r="I66" s="7"/>
     </row>
-    <row r="67" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A67" s="7">
         <v>2012</v>
       </c>
@@ -4097,7 +4103,7 @@
       </c>
       <c r="I67" s="7"/>
     </row>
-    <row r="68" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A68" s="7">
         <v>2012</v>
       </c>
@@ -4124,7 +4130,7 @@
       </c>
       <c r="I68" s="7"/>
     </row>
-    <row r="69" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A69" s="7">
         <v>2006</v>
       </c>
@@ -4201,7 +4207,7 @@
       </c>
       <c r="I71" s="7"/>
     </row>
-    <row r="72" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A72" s="7">
         <v>2013</v>
       </c>
@@ -4255,7 +4261,7 @@
       </c>
       <c r="I73" s="7"/>
     </row>
-    <row r="74" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A74" s="7">
         <v>2013</v>
       </c>
@@ -4282,7 +4288,7 @@
       </c>
       <c r="I74" s="7"/>
     </row>
-    <row r="75" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A75" s="7">
         <v>2013</v>
       </c>
@@ -4309,7 +4315,7 @@
       </c>
       <c r="I75" s="7"/>
     </row>
-    <row r="76" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A76" s="7">
         <v>2013</v>
       </c>
@@ -4384,7 +4390,7 @@
       </c>
       <c r="I78" s="7"/>
     </row>
-    <row r="79" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A79" s="7">
         <v>2013</v>
       </c>
@@ -4463,7 +4469,7 @@
       </c>
       <c r="I81" s="7"/>
     </row>
-    <row r="82" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A82" s="7">
         <v>2014</v>
       </c>
@@ -4592,7 +4598,7 @@
       </c>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A87" s="7">
         <v>2014</v>
       </c>
@@ -4698,7 +4704,7 @@
       </c>
       <c r="I90" s="7"/>
     </row>
-    <row r="91" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A91" s="7">
         <v>2014</v>
       </c>
@@ -4723,7 +4729,7 @@
       </c>
       <c r="I91" s="7"/>
     </row>
-    <row r="92" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A92" s="7">
         <v>2015</v>
       </c>
@@ -4777,7 +4783,7 @@
       </c>
       <c r="I93" s="7"/>
     </row>
-    <row r="94" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A94" s="7">
         <v>2015</v>
       </c>
@@ -4827,7 +4833,7 @@
       </c>
       <c r="I95" s="7"/>
     </row>
-    <row r="96" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A96" s="7">
         <v>2015</v>
       </c>
@@ -4879,7 +4885,7 @@
       </c>
       <c r="I97" s="7"/>
     </row>
-    <row r="98" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A98" s="7">
         <v>2015</v>
       </c>
@@ -4904,7 +4910,7 @@
       </c>
       <c r="I98" s="7"/>
     </row>
-    <row r="99" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A99" s="7">
         <v>2021</v>
       </c>
@@ -4981,7 +4987,7 @@
       </c>
       <c r="I101" s="7"/>
     </row>
-    <row r="102" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A102" s="7">
         <v>2015</v>
       </c>
@@ -5108,7 +5114,7 @@
       </c>
       <c r="I106" s="7"/>
     </row>
-    <row r="107" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A107" s="7">
         <v>2015</v>
       </c>
@@ -5133,7 +5139,7 @@
       </c>
       <c r="I107" s="7"/>
     </row>
-    <row r="108" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A108" s="7">
         <v>2016</v>
       </c>
@@ -5237,7 +5243,7 @@
       </c>
       <c r="I111" s="7"/>
     </row>
-    <row r="112" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A112" s="7">
         <v>2017</v>
       </c>
@@ -5264,7 +5270,7 @@
       </c>
       <c r="I112" s="7"/>
     </row>
-    <row r="113" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A113" s="7">
         <v>2017</v>
       </c>
@@ -5289,7 +5295,7 @@
       </c>
       <c r="I113" s="7"/>
     </row>
-    <row r="114" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A114" s="7">
         <v>2017</v>
       </c>
@@ -5339,7 +5345,7 @@
       </c>
       <c r="I115" s="7"/>
     </row>
-    <row r="116" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A116" s="7">
         <v>2017</v>
       </c>
@@ -5391,7 +5397,7 @@
       </c>
       <c r="I117" s="7"/>
     </row>
-    <row r="118" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A118" s="7">
         <v>2017</v>
       </c>
@@ -5416,7 +5422,7 @@
       </c>
       <c r="I118" s="7"/>
     </row>
-    <row r="119" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A119" s="7">
         <v>2017</v>
       </c>
@@ -5470,7 +5476,7 @@
       </c>
       <c r="I120" s="7"/>
     </row>
-    <row r="121" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A121" s="7">
         <v>2017</v>
       </c>
@@ -5524,7 +5530,7 @@
       </c>
       <c r="I122" s="7"/>
     </row>
-    <row r="123" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A123" s="7">
         <v>2017</v>
       </c>
@@ -5578,7 +5584,7 @@
       </c>
       <c r="I124" s="7"/>
     </row>
-    <row r="125" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A125" s="7">
         <v>2017</v>
       </c>
@@ -5707,7 +5713,7 @@
       </c>
       <c r="I129" s="7"/>
     </row>
-    <row r="130" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A130" s="7">
         <v>2018</v>
       </c>
@@ -5734,7 +5740,7 @@
       </c>
       <c r="I130" s="7"/>
     </row>
-    <row r="131" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A131" s="7">
         <v>2018</v>
       </c>
@@ -5786,7 +5792,7 @@
       </c>
       <c r="I132" s="7"/>
     </row>
-    <row r="133" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A133" s="7">
         <v>2011</v>
       </c>
@@ -5888,7 +5894,7 @@
       </c>
       <c r="I136" s="7"/>
     </row>
-    <row r="137" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A137" s="7">
         <v>2018</v>
       </c>
@@ -5915,7 +5921,7 @@
       </c>
       <c r="I137" s="7"/>
     </row>
-    <row r="138" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A138" s="7">
         <v>2012</v>
       </c>
@@ -5967,7 +5973,7 @@
       </c>
       <c r="I139" s="7"/>
     </row>
-    <row r="140" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A140" s="7">
         <v>2018</v>
       </c>
@@ -5992,7 +5998,7 @@
       </c>
       <c r="I140" s="7"/>
     </row>
-    <row r="141" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A141" s="7">
         <v>2018</v>
       </c>
@@ -6017,7 +6023,7 @@
       </c>
       <c r="I141" s="7"/>
     </row>
-    <row r="142" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A142" s="7">
         <v>2018</v>
       </c>
@@ -6121,7 +6127,7 @@
       </c>
       <c r="I145" s="7"/>
     </row>
-    <row r="146" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A146" s="7">
         <v>2019</v>
       </c>
@@ -6146,7 +6152,7 @@
       </c>
       <c r="I146" s="7"/>
     </row>
-    <row r="147" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A147" s="7">
         <v>2015</v>
       </c>
@@ -6171,7 +6177,7 @@
       </c>
       <c r="I147" s="7"/>
     </row>
-    <row r="148" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A148" s="7">
         <v>2006</v>
       </c>
@@ -6198,7 +6204,7 @@
       </c>
       <c r="I148" s="7"/>
     </row>
-    <row r="149" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A149" s="7">
         <v>2012</v>
       </c>
@@ -6252,7 +6258,7 @@
       </c>
       <c r="I150" s="7"/>
     </row>
-    <row r="151" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A151" s="7">
         <v>2019</v>
       </c>
@@ -6329,7 +6335,7 @@
       </c>
       <c r="I153" s="7"/>
     </row>
-    <row r="154" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A154" s="7">
         <v>2019</v>
       </c>
@@ -6381,7 +6387,7 @@
       </c>
       <c r="I155" s="7"/>
     </row>
-    <row r="156" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A156" s="7">
         <v>2012</v>
       </c>
@@ -6408,7 +6414,7 @@
       </c>
       <c r="I156" s="7"/>
     </row>
-    <row r="157" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A157" s="7">
         <v>2020</v>
       </c>
@@ -6458,7 +6464,7 @@
       </c>
       <c r="I158" s="7"/>
     </row>
-    <row r="159" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A159" s="7">
         <v>2020</v>
       </c>
@@ -6510,7 +6516,7 @@
       </c>
       <c r="I160" s="7"/>
     </row>
-    <row r="161" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A161" s="7">
         <v>2020</v>
       </c>
@@ -6537,7 +6543,7 @@
       </c>
       <c r="I161" s="7"/>
     </row>
-    <row r="162" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A162" s="7">
         <v>2020</v>
       </c>
@@ -6666,7 +6672,7 @@
       </c>
       <c r="I166" s="7"/>
     </row>
-    <row r="167" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A167" s="7">
         <v>2020</v>
       </c>
@@ -6718,7 +6724,7 @@
       </c>
       <c r="I168" s="7"/>
     </row>
-    <row r="169" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A169" s="7">
         <v>2020</v>
       </c>
@@ -6745,7 +6751,7 @@
       </c>
       <c r="I169" s="7"/>
     </row>
-    <row r="170" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A170" s="7">
         <v>2020</v>
       </c>
@@ -6799,7 +6805,7 @@
       </c>
       <c r="I171" s="7"/>
     </row>
-    <row r="172" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A172" s="7">
         <v>2020</v>
       </c>
@@ -6826,7 +6832,7 @@
       </c>
       <c r="I172" s="7"/>
     </row>
-    <row r="173" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A173" s="7">
         <v>2020</v>
       </c>
@@ -7038,7 +7044,7 @@
       </c>
       <c r="I180" s="7"/>
     </row>
-    <row r="181" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A181" s="7">
         <v>2021</v>
       </c>
@@ -7082,7 +7088,7 @@
       <c r="F182" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G182" s="15" t="s">
+      <c r="G182" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H182" s="7" t="s">
@@ -7090,7 +7096,7 @@
       </c>
       <c r="I182" s="7"/>
     </row>
-    <row r="183" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A183" s="7">
         <v>2021</v>
       </c>
@@ -7140,7 +7146,7 @@
       </c>
       <c r="I184" s="7"/>
     </row>
-    <row r="185" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A185" s="7">
         <v>2021</v>
       </c>
@@ -7219,7 +7225,7 @@
       </c>
       <c r="I187" s="7"/>
     </row>
-    <row r="188" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A188" s="7">
         <v>2021</v>
       </c>
@@ -7246,7 +7252,7 @@
       </c>
       <c r="I188" s="7"/>
     </row>
-    <row r="189" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A189" s="7">
         <v>2021</v>
       </c>
@@ -7298,7 +7304,7 @@
       </c>
       <c r="I190" s="7"/>
     </row>
-    <row r="191" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A191" s="7">
         <v>2021</v>
       </c>
@@ -7404,7 +7410,7 @@
       </c>
       <c r="I194" s="7"/>
     </row>
-    <row r="195" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A195" s="7">
         <v>2022</v>
       </c>
@@ -7431,7 +7437,7 @@
       </c>
       <c r="I195" s="7"/>
     </row>
-    <row r="196" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A196" s="7">
         <v>2022</v>
       </c>
@@ -7587,7 +7593,7 @@
       </c>
       <c r="I201" s="7"/>
     </row>
-    <row r="202" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A202" s="7">
         <v>2022</v>
       </c>
@@ -7793,7 +7799,7 @@
       </c>
       <c r="I209" s="7"/>
     </row>
-    <row r="210" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A210" s="7">
         <v>2023</v>
       </c>
@@ -7843,7 +7849,7 @@
       </c>
       <c r="I211" s="7"/>
     </row>
-    <row r="212" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A212" s="7">
         <v>2023</v>
       </c>
@@ -7920,7 +7926,7 @@
       </c>
       <c r="I214" s="7"/>
     </row>
-    <row r="215" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A215" s="7">
         <v>2023</v>
       </c>
@@ -7970,7 +7976,7 @@
       </c>
       <c r="I216" s="7"/>
     </row>
-    <row r="217" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A217" s="7">
         <v>2023</v>
       </c>
@@ -8027,6 +8033,7 @@
       <c r="B219" s="2" t="s">
         <v>458</v>
       </c>
+      <c r="C219" s="15"/>
       <c r="D219" s="2" t="s">
         <v>35</v>
       </c>
@@ -8193,7 +8200,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="226" spans="1:9" s="4" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:9" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.15">
       <c r="A226" s="7">
         <v>2024</v>
       </c>
@@ -8220,7 +8227,7 @@
       </c>
       <c r="I226" s="7"/>
     </row>
-    <row r="227" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" ht="43" x14ac:dyDescent="0.2">
       <c r="A227" s="7">
         <v>2024</v>
       </c>
@@ -8246,7 +8253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" ht="43" x14ac:dyDescent="0.2">
       <c r="A228" s="7">
         <v>2024</v>
       </c>
@@ -8329,7 +8336,7 @@
       <c r="B231" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C231" s="14" t="s">
+      <c r="C231" s="2" t="s">
         <v>545</v>
       </c>
       <c r="D231" s="2" t="s">
@@ -8384,10 +8391,10 @@
       <c r="C233" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D233" s="14" t="s">
+      <c r="D233" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="E233" s="14" t="s">
+      <c r="E233" s="2" t="s">
         <v>532</v>
       </c>
       <c r="F233" s="7" t="s">
@@ -8400,13 +8407,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" ht="29" x14ac:dyDescent="0.2">
       <c r="A234" s="7">
         <v>2024</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>507</v>
       </c>
+      <c r="C234" s="15"/>
       <c r="D234" s="2" t="s">
         <v>109</v>
       </c>
@@ -8423,7 +8431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" ht="29" x14ac:dyDescent="0.2">
       <c r="A235" s="7">
         <v>2024</v>
       </c>
@@ -8449,7 +8457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" ht="43" x14ac:dyDescent="0.2">
       <c r="A236" s="7">
         <v>2025</v>
       </c>
@@ -8476,283 +8484,283 @@
       </c>
     </row>
     <row r="237" spans="1:9" ht="29" x14ac:dyDescent="0.2">
-      <c r="A237" s="5">
+      <c r="A237" s="7">
         <v>2025</v>
       </c>
-      <c r="B237" s="14" t="s">
+      <c r="B237" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C237" s="14" t="s">
+      <c r="C237" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D237" s="14" t="s">
+      <c r="D237" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E237" s="14" t="s">
+      <c r="E237" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="F237" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G237" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H237" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A238" s="5">
+      <c r="F237" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G237" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H237" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+      <c r="A238" s="7">
         <v>2025</v>
       </c>
-      <c r="B238" s="14" t="s">
+      <c r="B238" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C238" s="14" t="s">
+      <c r="C238" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D238" s="14" t="s">
+      <c r="D238" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E238" s="14" t="s">
+      <c r="E238" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F238" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G238" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H238" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A239" s="5">
+      <c r="F238" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G238" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H238" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+      <c r="A239" s="7">
         <v>2025</v>
       </c>
-      <c r="B239" s="14" t="s">
+      <c r="B239" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="C239" s="12"/>
-      <c r="D239" s="14" t="s">
+      <c r="C239" s="15"/>
+      <c r="D239" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E239" s="14" t="s">
+      <c r="E239" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="F239" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G239" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H239" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="5">
+      <c r="F239" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G239" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H239" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
+      <c r="A240" s="7">
         <v>2025</v>
       </c>
-      <c r="B240" s="14" t="s">
+      <c r="B240" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C240" s="12"/>
-      <c r="D240" s="14" t="s">
+      <c r="C240" s="15"/>
+      <c r="D240" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E240" s="14" t="s">
+      <c r="E240" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F240" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G240" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H240" s="5" t="s">
+      <c r="F240" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G240" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H240" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
-      <c r="A241" s="5">
+      <c r="A241" s="7">
         <v>2025</v>
       </c>
-      <c r="B241" s="14" t="s">
+      <c r="B241" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C241" s="14" t="s">
+      <c r="C241" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D241" s="14" t="s">
+      <c r="D241" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E241" s="14" t="s">
+      <c r="E241" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="F241" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G241" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H241" s="5" t="s">
+      <c r="F241" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G241" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H241" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="242" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="5">
+      <c r="A242" s="7">
         <v>2025</v>
       </c>
-      <c r="B242" s="14" t="s">
+      <c r="B242" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C242" s="14" t="s">
+      <c r="C242" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D242" s="14" t="s">
+      <c r="D242" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E242" s="14" t="s">
+      <c r="E242" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="F242" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G242" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H242" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="5">
+      <c r="F242" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G242" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H242" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
+      <c r="A243" s="7">
         <v>2025</v>
       </c>
-      <c r="B243" s="14" t="s">
+      <c r="B243" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C243" s="14" t="s">
+      <c r="C243" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D243" s="14" t="s">
+      <c r="D243" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E243" s="14" t="s">
+      <c r="E243" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="F243" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G243" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H243" s="5" t="s">
+      <c r="F243" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G243" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H243" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A244" s="5">
+      <c r="A244" s="7">
         <v>2025</v>
       </c>
-      <c r="B244" s="14" t="s">
+      <c r="B244" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C244" s="14"/>
-      <c r="D244" s="14" t="s">
+      <c r="C244" s="2"/>
+      <c r="D244" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E244" s="14" t="s">
+      <c r="E244" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F244" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G244" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H244" s="5" t="s">
+      <c r="F244" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G244" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H244" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:9" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A245" s="5">
+      <c r="A245" s="7">
         <v>2025</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="B245" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="C245" s="5" t="s">
+      <c r="C245" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="D245" s="5" t="s">
+      <c r="D245" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E245" s="5" t="s">
+      <c r="E245" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F245" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G245" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H245" s="5" t="s">
+      <c r="F245" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G245" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H245" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="246" spans="1:9" ht="43" x14ac:dyDescent="0.2">
-      <c r="A246" s="5">
+      <c r="A246" s="7">
         <v>2025</v>
       </c>
-      <c r="B246" s="5" t="s">
+      <c r="B246" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="C246" s="14" t="s">
+      <c r="C246" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D246" s="5" t="s">
+      <c r="D246" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="E246" s="5" t="s">
+      <c r="E246" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="F246" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G246" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H246" s="5" t="s">
+      <c r="F246" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G246" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H246" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I246" s="6"/>
     </row>
-    <row r="247" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="5">
+    <row r="247" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="7">
         <v>2025</v>
       </c>
-      <c r="B247" s="5" t="s">
+      <c r="B247" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C247" s="5" t="s">
+      <c r="C247" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="D247" s="5" t="s">
+      <c r="D247" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E247" s="5" t="s">
+      <c r="E247" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="F247" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G247" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H247" s="5" t="s">
+      <c r="F247" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G247" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H247" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8831,6 +8839,32 @@
         <v>6</v>
       </c>
       <c r="H250" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+      <c r="A251" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F251" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G251" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H251" s="7" t="s">
         <v>6</v>
       </c>
     </row>

--- a/src/main/webapp/content/files/oncologyTherapies/fda_approved_oncology_therapies.xlsx
+++ b/src/main/webapp/content/files/oncologyTherapies/fda_approved_oncology_therapies.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luc2/MSK/oncokb/oncokb-pipeline/python/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cavendk1/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BF5860-F7FE-8141-A26A-832D3806CA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AB722C-EEB1-D245-AE68-66561FA255C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{D862B214-800F-AF40-9BAA-60FE1781D5C8}"/>
+    <workbookView xWindow="30760" yWindow="2320" windowWidth="29400" windowHeight="16900" xr2:uid="{D862B214-800F-AF40-9BAA-60FE1781D5C8}"/>
   </bookViews>
   <sheets>
     <sheet name="FDA-Approved Oncology Therapies" sheetId="1" r:id="rId1"/>
     <sheet name="Footnotes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FDA-Approved Oncology Therapies'!$A$1:$I$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FDA-Approved Oncology Therapies'!$A$1:$I$255</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="559">
   <si>
     <t>Year of drug’s first FDA- approval</t>
   </si>
@@ -166,9 +166,6 @@
     <t>Valrubicin</t>
   </si>
   <si>
-    <t>Anthracycline</t>
-  </si>
-  <si>
     <t>Fulvestrant</t>
   </si>
   <si>
@@ -1292,10 +1289,6 @@
   </si>
   <si>
     <t>IDH1 R132C/G/H/L/S</t>
-  </si>
-  <si>
-    <t>ESR1 Ligand-binding domain missense mutations and
-ER+/HER2-</t>
   </si>
   <si>
     <t>*FGFR2 Fusions
@@ -1342,9 +1335,6 @@
   </si>
   <si>
     <t>Gonadotropin-releasing hormone (GnRH) agonist</t>
-  </si>
-  <si>
-    <t>Asparagine specific-enzyme</t>
   </si>
   <si>
     <t>*Ph+ (BCR-ABL1 Fusion)
@@ -1366,10 +1356,6 @@
     <t>TSC1, TSC2 Oncogenic Mutations</t>
   </si>
   <si>
-    <t>Ph+ (BCR-ABL1 Fusion) or
-ABL1 T315I</t>
-  </si>
-  <si>
     <t>*MSI-H or dMMR
 *TMB-H
 *PD-L1-expressing
@@ -1388,10 +1374,6 @@
   <si>
     <t>*HER2+ (ERBB2 Amplifiaction)
 *KRAS and NRAS Wildtype and HER2+ (ERBB2 Amplification)</t>
-  </si>
-  <si>
-    <t>Ph+ (BCR-ABL1 Fusion)
-or ABL1 T315I</t>
   </si>
   <si>
     <t>FLT3 ITD Mutations</t>
@@ -1869,9 +1851,6 @@
     <t>Zongertinib</t>
   </si>
   <si>
-    <t>ERBB2 TKD activating mutations</t>
-  </si>
-  <si>
     <t>HER2 (ERBB2) inhibitor</t>
   </si>
   <si>
@@ -1900,10 +1879,111 @@
     <t>Trastuzumab deruxtecan + Pertuzumab</t>
   </si>
   <si>
-    <t>Antibody drug conjugate and monocolonal antibody</t>
-  </si>
-  <si>
     <t>HER2 (ERBB2)-directed antibody and topoisomerase inhibitor conjugate + anti-HER2 (ERBB2) antibody</t>
+  </si>
+  <si>
+    <t>Antibody drug conjugate and monocolonal antibody combination</t>
+  </si>
+  <si>
+    <t>Vepdegestrant</t>
+  </si>
+  <si>
+    <t>Heterobifunctional protein degrader</t>
+  </si>
+  <si>
+    <t>Sonrotoclax</t>
+  </si>
+  <si>
+    <t>Pivekimab sunirine</t>
+  </si>
+  <si>
+    <t>Proteolysis targeting chimera (PROTAC) and selective estrogen receptor degrader (SERD)</t>
+  </si>
+  <si>
+    <t>Relacorilant</t>
+  </si>
+  <si>
+    <t>Glucocorticoid receptor antagonist</t>
+  </si>
+  <si>
+    <t>Glucocorticoid receptor inhibitor</t>
+  </si>
+  <si>
+    <r>
+      <t>ERBB2 T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>yrosine kinase domain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> activating mutations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ERBB2 T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>yrosine kinase domain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> activating mutations</t>
+    </r>
+  </si>
+  <si>
+    <t>ESR1 Oncogenic missense mutations in the ligand-binding domain, V422del, L549P, or K303R and ER+/HER2-</t>
+  </si>
+  <si>
+    <t>CD123-directed antibody and alkylating agent conjugate</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ESR1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Oncogenic missense mutations in the ligand-binding domain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and ER+/HER2-</t>
+    </r>
+  </si>
+  <si>
+    <t>Ph+ (BCR-ABL1 Fusion) or ABL1 T315I</t>
   </si>
 </sst>
 </file>
@@ -2024,7 +2104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2053,8 +2133,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2371,7 +2454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B89377A-76F6-CA40-8081-AAD80BFAB6B8}">
-  <dimension ref="A1:I251"/>
+  <dimension ref="A1:I255"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" customWidth="1"/>
@@ -2387,16 +2470,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>1</v>
@@ -2405,7 +2488,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="I1" s="11"/>
     </row>
@@ -2467,7 +2550,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -2544,7 +2627,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>20</v>
@@ -2596,7 +2679,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>25</v>
@@ -2623,7 +2706,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>20</v>
@@ -2647,16 +2730,16 @@
         <v>2018</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>6</v>
@@ -2727,7 +2810,7 @@
         <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>38</v>
@@ -2758,7 +2841,7 @@
         <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>6</v>
@@ -2783,7 +2866,7 @@
         <v>13</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>7</v>
@@ -2801,16 +2884,16 @@
         <v>2002</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>6</v>
@@ -2828,14 +2911,14 @@
         <v>2002</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>6</v>
@@ -2853,7 +2936,7 @@
         <v>2002</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
@@ -2878,14 +2961,14 @@
         <v>2003</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>6</v>
@@ -2903,14 +2986,14 @@
         <v>2003</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>6</v>
@@ -2928,16 +3011,16 @@
         <v>2003</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>6</v>
@@ -2955,16 +3038,16 @@
         <v>2003</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>6</v>
@@ -2982,7 +3065,7 @@
         <v>2004</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
@@ -3007,14 +3090,14 @@
         <v>2004</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>6</v>
@@ -3032,16 +3115,16 @@
         <v>2004</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>6</v>
@@ -3059,7 +3142,7 @@
         <v>2004</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
@@ -3084,16 +3167,16 @@
         <v>2004</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>6</v>
@@ -3111,14 +3194,14 @@
         <v>2004</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>7</v>
@@ -3136,7 +3219,7 @@
         <v>2005</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
@@ -3164,7 +3247,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -3188,14 +3271,14 @@
         <v>2019</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>6</v>
@@ -3208,12 +3291,12 @@
       </c>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7">
         <v>2006</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
@@ -3238,7 +3321,7 @@
         <v>2006</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
@@ -3263,16 +3346,16 @@
         <v>2006</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>6</v>
@@ -3290,16 +3373,16 @@
         <v>2019</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>6</v>
@@ -3317,14 +3400,14 @@
         <v>2006</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>6</v>
@@ -3342,14 +3425,14 @@
         <v>2007</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>7</v>
@@ -3367,16 +3450,16 @@
         <v>2007</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>6</v>
@@ -3394,16 +3477,16 @@
         <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>6</v>
@@ -3421,14 +3504,14 @@
         <v>2007</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>6</v>
@@ -3446,7 +3529,7 @@
         <v>2008</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
@@ -3471,14 +3554,14 @@
         <v>2008</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>6</v>
@@ -3496,16 +3579,16 @@
         <v>2009</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>6</v>
@@ -3523,14 +3606,14 @@
         <v>2009</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>6</v>
@@ -3548,14 +3631,14 @@
         <v>2019</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>6</v>
@@ -3573,14 +3656,14 @@
         <v>2009</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>7</v>
@@ -3598,14 +3681,14 @@
         <v>2009</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>6</v>
@@ -3623,14 +3706,14 @@
         <v>2010</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>7</v>
@@ -3648,14 +3731,14 @@
         <v>2010</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>7</v>
@@ -3673,14 +3756,14 @@
         <v>2010</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>7</v>
@@ -3698,14 +3781,14 @@
         <v>2011</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>6</v>
@@ -3723,14 +3806,14 @@
         <v>2011</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>7</v>
@@ -3748,16 +3831,16 @@
         <v>2011</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>6</v>
@@ -3775,16 +3858,16 @@
         <v>2020</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>6</v>
@@ -3802,14 +3885,14 @@
         <v>2011</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>6</v>
@@ -3827,14 +3910,14 @@
         <v>2011</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>7</v>
@@ -3852,14 +3935,14 @@
         <v>2011</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>6</v>
@@ -3877,16 +3960,16 @@
         <v>2019</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>6</v>
@@ -3904,16 +3987,16 @@
         <v>2011</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>6</v>
@@ -3931,14 +4014,14 @@
         <v>2012</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>6</v>
@@ -3956,14 +4039,14 @@
         <v>2012</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>6</v>
@@ -3981,14 +4064,14 @@
         <v>2021</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>6</v>
@@ -4006,16 +4089,16 @@
         <v>2023</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>6</v>
@@ -4033,14 +4116,14 @@
         <v>2012</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>6</v>
@@ -4058,14 +4141,14 @@
         <v>2012</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>6</v>
@@ -4083,14 +4166,14 @@
         <v>2012</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>6</v>
@@ -4108,16 +4191,16 @@
         <v>2012</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>6</v>
@@ -4135,16 +4218,16 @@
         <v>2006</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>6</v>
@@ -4162,14 +4245,14 @@
         <v>2005</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>6</v>
@@ -4187,14 +4270,14 @@
         <v>2012</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>6</v>
@@ -4212,16 +4295,16 @@
         <v>2013</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>6</v>
@@ -4239,16 +4322,16 @@
         <v>2013</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>6</v>
@@ -4266,16 +4349,16 @@
         <v>2013</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>6</v>
@@ -4293,16 +4376,16 @@
         <v>2013</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>6</v>
@@ -4320,14 +4403,14 @@
         <v>2013</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>6</v>
@@ -4345,14 +4428,14 @@
         <v>2013</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>7</v>
@@ -4370,14 +4453,14 @@
         <v>2013</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>7</v>
@@ -4395,16 +4478,16 @@
         <v>2013</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>6</v>
@@ -4422,14 +4505,14 @@
         <v>2014</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>6</v>
@@ -4447,16 +4530,16 @@
         <v>2014</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>6</v>
@@ -4474,16 +4557,16 @@
         <v>2014</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>6</v>
@@ -4501,16 +4584,16 @@
         <v>2014</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D83" s="2" t="s">
+      <c r="E83" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>6</v>
@@ -4528,14 +4611,14 @@
         <v>2014</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>6</v>
@@ -4553,14 +4636,14 @@
         <v>2014</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>6</v>
@@ -4578,14 +4661,14 @@
         <v>2014</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>7</v>
@@ -4603,16 +4686,16 @@
         <v>2014</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>6</v>
@@ -4630,16 +4713,16 @@
         <v>2014</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>6</v>
@@ -4657,16 +4740,16 @@
         <v>2014</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>6</v>
@@ -4684,14 +4767,14 @@
         <v>2014</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>6</v>
@@ -4709,14 +4792,14 @@
         <v>2014</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>7</v>
@@ -4734,16 +4817,16 @@
         <v>2015</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>6</v>
@@ -4761,16 +4844,16 @@
         <v>2015</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D93" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>6</v>
@@ -4788,14 +4871,14 @@
         <v>2015</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>6</v>
@@ -4813,14 +4896,14 @@
         <v>2015</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>6</v>
@@ -4838,14 +4921,14 @@
         <v>2015</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>6</v>
@@ -4863,16 +4946,16 @@
         <v>2015</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="F97" s="7" t="s">
         <v>6</v>
@@ -4890,14 +4973,14 @@
         <v>2015</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>6</v>
@@ -4915,14 +4998,14 @@
         <v>2021</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>6</v>
@@ -4940,14 +5023,14 @@
         <v>2015</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>6</v>
@@ -4965,16 +5048,16 @@
         <v>2015</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>6</v>
@@ -4992,16 +5075,16 @@
         <v>2015</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>6</v>
@@ -5019,14 +5102,14 @@
         <v>2015</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>6</v>
@@ -5044,14 +5127,14 @@
         <v>2015</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>6</v>
@@ -5069,14 +5152,14 @@
         <v>2015</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>7</v>
@@ -5094,7 +5177,7 @@
         <v>2015</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
@@ -5119,14 +5202,14 @@
         <v>2015</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>7</v>
@@ -5144,16 +5227,16 @@
         <v>2016</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>6</v>
@@ -5171,14 +5254,14 @@
         <v>2016</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>6</v>
@@ -5196,16 +5279,16 @@
         <v>2016</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>6</v>
@@ -5223,14 +5306,14 @@
         <v>2016</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>6</v>
@@ -5248,16 +5331,16 @@
         <v>2017</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>6</v>
@@ -5275,14 +5358,14 @@
         <v>2017</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>6</v>
@@ -5300,14 +5383,14 @@
         <v>2017</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>6</v>
@@ -5325,14 +5408,14 @@
         <v>2017</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>6</v>
@@ -5350,16 +5433,16 @@
         <v>2017</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>6</v>
@@ -5377,14 +5460,14 @@
         <v>2017</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>6</v>
@@ -5402,14 +5485,14 @@
         <v>2017</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>7</v>
@@ -5427,16 +5510,16 @@
         <v>2017</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>6</v>
@@ -5454,16 +5537,16 @@
         <v>2017</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>6</v>
@@ -5481,16 +5564,16 @@
         <v>2017</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>6</v>
@@ -5508,16 +5591,16 @@
         <v>2011</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>6</v>
@@ -5535,16 +5618,16 @@
         <v>2017</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>6</v>
@@ -5562,16 +5645,16 @@
         <v>2017</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>6</v>
@@ -5589,16 +5672,16 @@
         <v>2017</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>6</v>
@@ -5616,14 +5699,14 @@
         <v>2017</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>6</v>
@@ -5641,14 +5724,14 @@
         <v>2018</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>6</v>
@@ -5666,16 +5749,16 @@
         <v>2018</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D128" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>6</v>
@@ -5693,14 +5776,14 @@
         <v>2018</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="F129" s="7" t="s">
         <v>7</v>
@@ -5718,16 +5801,16 @@
         <v>2018</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F130" s="7" t="s">
         <v>6</v>
@@ -5745,16 +5828,16 @@
         <v>2018</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D131" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="F131" s="7" t="s">
         <v>6</v>
@@ -5772,14 +5855,14 @@
         <v>2018</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F132" s="7" t="s">
         <v>6</v>
@@ -5797,14 +5880,14 @@
         <v>2011</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>6</v>
@@ -5822,14 +5905,14 @@
         <v>2018</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F134" s="7" t="s">
         <v>6</v>
@@ -5847,14 +5930,14 @@
         <v>2018</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F135" s="7" t="s">
         <v>7</v>
@@ -5872,16 +5955,16 @@
         <v>2018</v>
       </c>
       <c r="B136" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>6</v>
@@ -5899,16 +5982,16 @@
         <v>2018</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F137" s="7" t="s">
         <v>6</v>
@@ -5926,14 +6009,14 @@
         <v>2012</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F138" s="7" t="s">
         <v>6</v>
@@ -5951,16 +6034,16 @@
         <v>2018</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F139" s="7" t="s">
         <v>6</v>
@@ -5978,14 +6061,14 @@
         <v>2018</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F140" s="7" t="s">
         <v>7</v>
@@ -6003,14 +6086,14 @@
         <v>2018</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F141" s="7" t="s">
         <v>6</v>
@@ -6028,14 +6111,14 @@
         <v>2018</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F142" s="7" t="s">
         <v>6</v>
@@ -6053,16 +6136,16 @@
         <v>2018</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F143" s="7" t="s">
         <v>6</v>
@@ -6080,16 +6163,16 @@
         <v>2019</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D144" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D144" s="2" t="s">
+      <c r="E144" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="F144" s="7" t="s">
         <v>6</v>
@@ -6107,14 +6190,14 @@
         <v>2019</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F145" s="7" t="s">
         <v>6</v>
@@ -6132,14 +6215,14 @@
         <v>2019</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F146" s="7" t="s">
         <v>6</v>
@@ -6157,14 +6240,14 @@
         <v>2015</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F147" s="7" t="s">
         <v>6</v>
@@ -6182,16 +6265,16 @@
         <v>2006</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F148" s="7" t="s">
         <v>6</v>
@@ -6209,16 +6292,16 @@
         <v>2012</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F149" s="7" t="s">
         <v>6</v>
@@ -6236,16 +6319,16 @@
         <v>2007</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F150" s="7" t="s">
         <v>6</v>
@@ -6263,14 +6346,14 @@
         <v>2019</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F151" s="7" t="s">
         <v>6</v>
@@ -6288,14 +6371,14 @@
         <v>2019</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F152" s="7" t="s">
         <v>6</v>
@@ -6313,16 +6396,16 @@
         <v>2019</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="F153" s="7" t="s">
         <v>6</v>
@@ -6340,14 +6423,14 @@
         <v>2019</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F154" s="7" t="s">
         <v>6</v>
@@ -6365,16 +6448,16 @@
         <v>2020</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D155" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D155" s="2" t="s">
+      <c r="E155" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F155" s="7" t="s">
         <v>6</v>
@@ -6392,16 +6475,16 @@
         <v>2012</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>438</v>
+        <v>558</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F156" s="7" t="s">
         <v>6</v>
@@ -6419,14 +6502,14 @@
         <v>2020</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F157" s="7" t="s">
         <v>6</v>
@@ -6444,14 +6527,14 @@
         <v>2020</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E158" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="F158" s="7" t="s">
         <v>6</v>
@@ -6469,16 +6552,16 @@
         <v>2020</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="F159" s="7" t="s">
         <v>6</v>
@@ -6496,14 +6579,14 @@
         <v>2020</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F160" s="7" t="s">
         <v>7</v>
@@ -6521,16 +6604,16 @@
         <v>2020</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D161" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="E161" s="2" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="F161" s="7" t="s">
         <v>6</v>
@@ -6548,14 +6631,14 @@
         <v>2020</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F162" s="7" t="s">
         <v>6</v>
@@ -6573,7 +6656,7 @@
         <v>2020</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
@@ -6598,10 +6681,10 @@
         <v>2020</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>38</v>
@@ -6625,14 +6708,14 @@
         <v>2020</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F165" s="7" t="s">
         <v>6</v>
@@ -6650,16 +6733,16 @@
         <v>2020</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F166" s="7" t="s">
         <v>6</v>
@@ -6677,16 +6760,16 @@
         <v>2020</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="F167" s="7" t="s">
         <v>6</v>
@@ -6704,14 +6787,14 @@
         <v>2020</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F168" s="7" t="s">
         <v>6</v>
@@ -6729,16 +6812,16 @@
         <v>2020</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E169" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="F169" s="7" t="s">
         <v>6</v>
@@ -6756,16 +6839,16 @@
         <v>2020</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F170" s="7" t="s">
         <v>6</v>
@@ -6783,16 +6866,16 @@
         <v>2020</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E171" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="F171" s="7" t="s">
         <v>6</v>
@@ -6810,16 +6893,16 @@
         <v>2020</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F172" s="7" t="s">
         <v>6</v>
@@ -6837,14 +6920,14 @@
         <v>2020</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F173" s="7" t="s">
         <v>6</v>
@@ -6862,16 +6945,16 @@
         <v>2020</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E174" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="F174" s="7" t="s">
         <v>6</v>
@@ -6889,16 +6972,16 @@
         <v>2020</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="F175" s="7" t="s">
         <v>6</v>
@@ -6916,16 +6999,16 @@
         <v>2021</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F176" s="7" t="s">
         <v>6</v>
@@ -6943,16 +7026,16 @@
         <v>2021</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="F177" s="7" t="s">
         <v>6</v>
@@ -6970,16 +7053,16 @@
         <v>2021</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="F178" s="7" t="s">
         <v>6</v>
@@ -6997,16 +7080,16 @@
         <v>2021</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="F179" s="7" t="s">
         <v>6</v>
@@ -7024,14 +7107,14 @@
         <v>2021</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F180" s="7" t="s">
         <v>6</v>
@@ -7049,16 +7132,16 @@
         <v>2021</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F181" s="7" t="s">
         <v>6</v>
@@ -7076,14 +7159,14 @@
         <v>2021</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E182" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="F182" s="7" t="s">
         <v>6</v>
@@ -7101,14 +7184,14 @@
         <v>2021</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F183" s="7" t="s">
         <v>6</v>
@@ -7126,7 +7209,7 @@
         <v>2021</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
@@ -7151,16 +7234,16 @@
         <v>2021</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="F185" s="7" t="s">
         <v>6</v>
@@ -7178,14 +7261,14 @@
         <v>2021</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="F186" s="7" t="s">
         <v>6</v>
@@ -7203,16 +7286,16 @@
         <v>2021</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="F187" s="7" t="s">
         <v>6</v>
@@ -7230,16 +7313,16 @@
         <v>2021</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F188" s="7" t="s">
         <v>6</v>
@@ -7257,14 +7340,14 @@
         <v>2021</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F189" s="7" t="s">
         <v>6</v>
@@ -7282,16 +7365,16 @@
         <v>2012</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F190" s="7" t="s">
         <v>6</v>
@@ -7309,16 +7392,16 @@
         <v>2021</v>
       </c>
       <c r="B191" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D191" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C191" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D191" s="2" t="s">
+      <c r="E191" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="F191" s="7" t="s">
         <v>6</v>
@@ -7336,16 +7419,16 @@
         <v>2018</v>
       </c>
       <c r="B192" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="F192" s="7" t="s">
         <v>6</v>
@@ -7363,16 +7446,16 @@
         <v>2022</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F193" s="7" t="s">
         <v>6</v>
@@ -7390,14 +7473,14 @@
         <v>2022</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F194" s="7" t="s">
         <v>6</v>
@@ -7415,16 +7498,16 @@
         <v>2022</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F195" s="7" t="s">
         <v>6</v>
@@ -7442,16 +7525,16 @@
         <v>2022</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="F196" s="7" t="s">
         <v>6</v>
@@ -7469,14 +7552,14 @@
         <v>2022</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F197" s="7" t="s">
         <v>6</v>
@@ -7494,14 +7577,14 @@
         <v>2022</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="F198" s="7" t="s">
         <v>6</v>
@@ -7519,14 +7602,14 @@
         <v>2022</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F199" s="7" t="s">
         <v>6</v>
@@ -7544,16 +7627,16 @@
         <v>2022</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F200" s="7" t="s">
         <v>6</v>
@@ -7571,16 +7654,16 @@
         <v>2022</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="F201" s="7" t="s">
         <v>6</v>
@@ -7598,16 +7681,16 @@
         <v>2022</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E202" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="F202" s="7" t="s">
         <v>6</v>
@@ -7625,14 +7708,14 @@
         <v>2022</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F203" s="7" t="s">
         <v>6</v>
@@ -7650,14 +7733,14 @@
         <v>2022</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>6</v>
@@ -7675,16 +7758,16 @@
         <v>2023</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E205" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>6</v>
@@ -7702,16 +7785,16 @@
         <v>2023</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>418</v>
+        <v>557</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F206" s="7" t="s">
         <v>6</v>
@@ -7729,14 +7812,14 @@
         <v>2023</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F207" s="7" t="s">
         <v>6</v>
@@ -7754,14 +7837,14 @@
         <v>2023</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="F208" s="7" t="s">
         <v>6</v>
@@ -7779,14 +7862,14 @@
         <v>2023</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F209" s="7" t="s">
         <v>6</v>
@@ -7804,14 +7887,14 @@
         <v>2023</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F210" s="7" t="s">
         <v>6</v>
@@ -7829,14 +7912,14 @@
         <v>2023</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F211" s="7" t="s">
         <v>6</v>
@@ -7854,14 +7937,14 @@
         <v>2023</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F212" s="7" t="s">
         <v>6</v>
@@ -7879,16 +7962,16 @@
         <v>2023</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="F213" s="7" t="s">
         <v>6</v>
@@ -7906,14 +7989,14 @@
         <v>2009</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F214" s="7" t="s">
         <v>6</v>
@@ -7931,14 +8014,14 @@
         <v>2023</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F215" s="7" t="s">
         <v>6</v>
@@ -7956,14 +8039,14 @@
         <v>2023</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F216" s="7" t="s">
         <v>6</v>
@@ -7981,14 +8064,14 @@
         <v>2023</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F217" s="7" t="s">
         <v>6</v>
@@ -8006,14 +8089,14 @@
         <v>2023</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F218" s="7" t="s">
         <v>6</v>
@@ -8031,14 +8114,13 @@
         <v>2024</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C219" s="15"/>
+        <v>453</v>
+      </c>
       <c r="D219" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F219" s="7" t="s">
         <v>6</v>
@@ -8055,14 +8137,14 @@
         <v>2024</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C220" s="13"/>
       <c r="D220" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F220" s="7" t="s">
         <v>6</v>
@@ -8079,16 +8161,16 @@
         <v>2024</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="F221" s="7" t="s">
         <v>6</v>
@@ -8105,14 +8187,14 @@
         <v>2024</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F222" s="7" t="s">
         <v>6</v>
@@ -8129,14 +8211,14 @@
         <v>2024</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F223" s="7" t="s">
         <v>6</v>
@@ -8153,16 +8235,16 @@
         <v>2024</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>6</v>
@@ -8179,16 +8261,16 @@
         <v>2024</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>6</v>
@@ -8205,16 +8287,16 @@
         <v>2024</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="F226" s="7" t="s">
         <v>6</v>
@@ -8232,16 +8314,16 @@
         <v>2024</v>
       </c>
       <c r="B227" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C227" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="C227" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="D227" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F227" s="7" t="s">
         <v>6</v>
@@ -8258,16 +8340,16 @@
         <v>2024</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="F228" s="7" t="s">
         <v>6</v>
@@ -8284,16 +8366,16 @@
         <v>2024</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F229" s="7" t="s">
         <v>6</v>
@@ -8310,14 +8392,14 @@
         <v>2024</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F230" s="7" t="s">
         <v>6</v>
@@ -8334,16 +8416,16 @@
         <v>2024</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>545</v>
+        <v>491</v>
+      </c>
+      <c r="C231" s="14" t="s">
+        <v>539</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F231" s="7" t="s">
         <v>6</v>
@@ -8360,10 +8442,10 @@
         <v>2024</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>38</v>
@@ -8386,16 +8468,16 @@
         <v>2024</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>532</v>
+        <v>494</v>
+      </c>
+      <c r="D233" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="E233" s="14" t="s">
+        <v>527</v>
       </c>
       <c r="F233" s="7" t="s">
         <v>6</v>
@@ -8412,14 +8494,13 @@
         <v>2024</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="C234" s="15"/>
+        <v>502</v>
+      </c>
       <c r="D234" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F234" s="7" t="s">
         <v>6</v>
@@ -8436,16 +8517,16 @@
         <v>2024</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F235" s="7" t="s">
         <v>6</v>
@@ -8462,305 +8543,305 @@
         <v>2025</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F236" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G236" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H236" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+      <c r="A237" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B237" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="C237" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="D237" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E237" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H237" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+      <c r="A238" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B238" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="C238" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="D238" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E238" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H238" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+      <c r="A239" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B239" s="14" t="s">
+        <v>510</v>
+      </c>
+      <c r="C239" s="12"/>
+      <c r="D239" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E239" s="14" t="s">
         <v>511</v>
       </c>
-      <c r="C236" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F236" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G236" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H236" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" ht="29" x14ac:dyDescent="0.2">
-      <c r="A237" s="7">
+      <c r="F239" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H239" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
+      <c r="A240" s="5">
         <v>2025</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C237" s="2" t="s">
+      <c r="B240" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C240" s="12"/>
+      <c r="D240" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E240" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
+      <c r="A241" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B241" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="C241" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="D241" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H241" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B242" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="C242" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="D242" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E242" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H242" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
+      <c r="A243" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B243" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="C243" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="D243" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E243" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H243" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A244" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B244" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="C244" s="14"/>
+      <c r="D244" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E244" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G244" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H244" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+      <c r="A245" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D245" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H245" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="43" x14ac:dyDescent="0.2">
+      <c r="A246" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B246" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F237" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G237" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H237" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" ht="29" x14ac:dyDescent="0.2">
-      <c r="A238" s="7">
+      <c r="C246" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="D246" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="E246" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G246" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H246" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I246" s="6"/>
+    </row>
+    <row r="247" spans="1:9" s="15" customFormat="1" ht="29" x14ac:dyDescent="0.2">
+      <c r="A247" s="5">
         <v>2025</v>
       </c>
-      <c r="B238" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F238" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G238" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H238" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" ht="29" x14ac:dyDescent="0.2">
-      <c r="A239" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C239" s="15"/>
-      <c r="D239" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F239" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G239" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H239" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
-      <c r="A240" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C240" s="15"/>
-      <c r="D240" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F240" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G240" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H240" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
-      <c r="A241" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F241" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G241" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H241" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F242" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G242" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H242" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
-      <c r="A243" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F243" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G243" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H243" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A244" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F244" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G244" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H244" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.15">
-      <c r="A245" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B245" s="7" t="s">
+      <c r="B247" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="C245" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="D245" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E245" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F245" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G245" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H245" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" ht="43" x14ac:dyDescent="0.2">
-      <c r="A246" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B246" s="7" t="s">
+      <c r="C247" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="D247" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E247" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="C246" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D246" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="E246" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="F246" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G246" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H246" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I246" s="6"/>
-    </row>
-    <row r="247" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B247" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="C247" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="D247" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E247" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="F247" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G247" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H247" s="7" t="s">
+      <c r="F247" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H247" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8769,16 +8850,16 @@
         <v>2025</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D248" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F248" s="7" t="s">
         <v>6</v>
@@ -8795,16 +8876,16 @@
         <v>2025</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>6</v>
@@ -8816,60 +8897,158 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" spans="1:9" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:9" s="7" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A250" s="7">
         <v>2025</v>
       </c>
       <c r="B250" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E250" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F250" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G250" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H250" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+      <c r="A251" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B251" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="C251" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="D251" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="E251" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H251" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
+      <c r="A252" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B252" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="C252" s="16"/>
+      <c r="D252" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="E252" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="F252" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G252" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H252" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" s="9" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A253" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B253" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="C253" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="D253" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="E253" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="F253" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G253" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H253" s="16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B254" s="16" t="s">
         <v>547</v>
       </c>
-      <c r="C250" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="D250" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E250" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="F250" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G250" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H250" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.15">
-      <c r="A251" s="7">
-        <v>2025</v>
-      </c>
-      <c r="B251" s="2" t="s">
+      <c r="C254" s="16"/>
+      <c r="D254" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E254" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="F254" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G254" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H254" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B255" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="C251" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F251" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G251" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H251" s="7" t="s">
-        <v>6</v>
+      <c r="C255" s="16"/>
+      <c r="D255" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E255" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="F255" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G255" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H255" s="16" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I247" xr:uid="{6B89377A-76F6-CA40-8081-AAD80BFAB6B8}"/>
+  <autoFilter ref="A1:I255" xr:uid="{6B89377A-76F6-CA40-8081-AAD80BFAB6B8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H217">
     <sortCondition ref="B2:B217"/>
   </sortState>
@@ -8888,37 +9067,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="59" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/webapp/content/files/oncologyTherapies/fda_approved_oncology_therapies.xlsx
+++ b/src/main/webapp/content/files/oncologyTherapies/fda_approved_oncology_therapies.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cavendk1/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cavendk1/Documents/New onc therapies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AB722C-EEB1-D245-AE68-66561FA255C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F9BA2ED-E9F5-C248-BD05-3C08F26C007D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30760" yWindow="2320" windowWidth="29400" windowHeight="16900" xr2:uid="{D862B214-800F-AF40-9BAA-60FE1781D5C8}"/>
+    <workbookView xWindow="30800" yWindow="-5980" windowWidth="40000" windowHeight="24420" xr2:uid="{D862B214-800F-AF40-9BAA-60FE1781D5C8}"/>
   </bookViews>
   <sheets>
     <sheet name="FDA-Approved Oncology Therapies" sheetId="1" r:id="rId1"/>
     <sheet name="Footnotes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FDA-Approved Oncology Therapies'!$A$1:$I$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FDA-Approved Oncology Therapies'!$A$1:$I$263</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="581">
   <si>
     <t>Year of drug’s first FDA- approval</t>
   </si>
@@ -166,6 +166,9 @@
     <t>Valrubicin</t>
   </si>
   <si>
+    <t>Anthracycline</t>
+  </si>
+  <si>
     <t>Fulvestrant</t>
   </si>
   <si>
@@ -1084,12 +1087,6 @@
     <t>Anti-PD-1 antibody + Anti-LAG-3 antibody</t>
   </si>
   <si>
-    <t>Pluvicto</t>
-  </si>
-  <si>
-    <t>Radioligand therapeutic agent</t>
-  </si>
-  <si>
     <t>Tebentafusp</t>
   </si>
   <si>
@@ -1289,6 +1286,10 @@
   </si>
   <si>
     <t>IDH1 R132C/G/H/L/S</t>
+  </si>
+  <si>
+    <t>ESR1 Ligand-binding domain missense mutations and
+ER+/HER2-</t>
   </si>
   <si>
     <t>*FGFR2 Fusions
@@ -1335,6 +1336,9 @@
   </si>
   <si>
     <t>Gonadotropin-releasing hormone (GnRH) agonist</t>
+  </si>
+  <si>
+    <t>Asparagine specific-enzyme</t>
   </si>
   <si>
     <t>*Ph+ (BCR-ABL1 Fusion)
@@ -1356,6 +1360,10 @@
     <t>TSC1, TSC2 Oncogenic Mutations</t>
   </si>
   <si>
+    <t>Ph+ (BCR-ABL1 Fusion) or
+ABL1 T315I</t>
+  </si>
+  <si>
     <t>*MSI-H or dMMR
 *TMB-H
 *PD-L1-expressing
@@ -1376,10 +1384,11 @@
 *KRAS and NRAS Wildtype and HER2+ (ERBB2 Amplification)</t>
   </si>
   <si>
+    <t>Ph+ (BCR-ABL1 Fusion)
+or ABL1 T315I</t>
+  </si>
+  <si>
     <t>FLT3 ITD Mutations</t>
-  </si>
-  <si>
-    <t>PIK3CA, AKT1 or PTEN Oncogenic Mutations and HR+/HER2-</t>
   </si>
   <si>
     <t>KIT/PDGFRA inhibitor</t>
@@ -1851,6 +1860,9 @@
     <t>Zongertinib</t>
   </si>
   <si>
+    <t>ERBB2 TKD activating mutations</t>
+  </si>
+  <si>
     <t>HER2 (ERBB2) inhibitor</t>
   </si>
   <si>
@@ -1882,66 +1894,63 @@
     <t>HER2 (ERBB2)-directed antibody and topoisomerase inhibitor conjugate + anti-HER2 (ERBB2) antibody</t>
   </si>
   <si>
+    <t>Relacorilant + Nab-paclitaxel</t>
+  </si>
+  <si>
+    <t>Glucocorticoid receptor antagonist and taxane combination</t>
+  </si>
+  <si>
     <t>Antibody drug conjugate and monocolonal antibody combination</t>
   </si>
   <si>
+    <t>Glucocorticoid receptor inhibitor + antimicrotubule agent</t>
+  </si>
+  <si>
     <t>Vepdegestrant</t>
   </si>
   <si>
     <t>Heterobifunctional protein degrader</t>
   </si>
   <si>
+    <t>ER+/HER2-/ESR1 mutant</t>
+  </si>
+  <si>
     <t>Sonrotoclax</t>
   </si>
   <si>
     <t>Pivekimab sunirine</t>
   </si>
   <si>
+    <t>D123-directed antibody and alkylating agent conjugate</t>
+  </si>
+  <si>
     <t>Proteolysis targeting chimera (PROTAC) and selective estrogen receptor degrader (SERD)</t>
   </si>
   <si>
-    <t>Relacorilant</t>
-  </si>
-  <si>
-    <t>Glucocorticoid receptor antagonist</t>
-  </si>
-  <si>
-    <t>Glucocorticoid receptor inhibitor</t>
+    <t>ER+/HER2-/PIK3CA wildtype</t>
+  </si>
+  <si>
+    <t>Multi-targeted kinase inhibitor (targets include PI3Kα/β/δ/γ and mTORC1/2)</t>
+  </si>
+  <si>
+    <t>Zidesamitinib</t>
+  </si>
+  <si>
+    <t>Lutetium Lu 177 vipivotide tetraxetan</t>
+  </si>
+  <si>
+    <t>PSMA-directed radioactive therapeutic agent</t>
+  </si>
+  <si>
+    <t>Vusolimogene oderparepvec</t>
+  </si>
+  <si>
+    <t>Immunomodulatory drug; cereblon E3 ligase modulator + anti-CD38 antibody</t>
   </si>
   <si>
     <r>
-      <t>ERBB2 T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>yrosine kinase domain</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> activating mutations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ERBB2 T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>yrosine kinase domain</t>
+      <t xml:space="preserve">*PIK3CA, AKT1 or PTEN Oncogenic Mutations and HR+/HER2-
+</t>
     </r>
     <r>
       <rPr>
@@ -1950,40 +1959,53 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> activating mutations</t>
+      <t>*PTEN-deficient</t>
     </r>
   </si>
   <si>
-    <t>ESR1 Oncogenic missense mutations in the ligand-binding domain, V422del, L549P, or K303R and ER+/HER2-</t>
-  </si>
-  <si>
-    <t>CD123-directed antibody and alkylating agent conjugate</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ESR1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Oncogenic missense mutations in the ligand-binding domain</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and ER+/HER2-</t>
-    </r>
-  </si>
-  <si>
-    <t>Ph+ (BCR-ABL1 Fusion) or ABL1 T315I</t>
+    <t>Gedatolisib + Fulvestrant +/- Palbociclib</t>
+  </si>
+  <si>
+    <t>Sacituzumab govitecan + Pembrolizumab</t>
+  </si>
+  <si>
+    <t>Belzutifan + Pembrolizumab</t>
+  </si>
+  <si>
+    <t>TROP2-directed antibody and topoisomerase inhibitor conjugate + anti-PD-1 antibody</t>
+  </si>
+  <si>
+    <t>Other immunotherapy and hematopoietic protein binding antibody, ADC or cytotoxin combination</t>
+  </si>
+  <si>
+    <t>HR+/ HER2+ (ERBB2 Amplification)</t>
+  </si>
+  <si>
+    <t>CDK4/6 inhibitor + anti-HER2 (ERBB2) antibodies</t>
+  </si>
+  <si>
+    <t>Palbociclib + Trastuzumab +/- Pertuzumab</t>
+  </si>
+  <si>
+    <t>Small molecule inhibitor and immune checkpoint inhibitor combination </t>
+  </si>
+  <si>
+    <t>HIF-2ɑ inhibitor + anti-PD-1 antibody</t>
+  </si>
+  <si>
+    <t>Teclistamab + Daratumumab</t>
+  </si>
+  <si>
+    <t>Bispecific T-cell engager and hematopoietic protein binding antibody, ADC or cytotoxin combination</t>
+  </si>
+  <si>
+    <t>Bispecific BCMA-directed CD3 T-cell engager + anti-CD38 antibody</t>
+  </si>
+  <si>
+    <t>Zanidatamab + Tislelizumab</t>
+  </si>
+  <si>
+    <t>Iberdomide + Daratumumab</t>
   </si>
 </sst>
 </file>
@@ -2026,7 +2048,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2043,7 +2065,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2454,7 +2476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B89377A-76F6-CA40-8081-AAD80BFAB6B8}">
-  <dimension ref="A1:I255"/>
+  <dimension ref="A1:K267"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" customWidth="1"/>
@@ -2470,16 +2492,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>1</v>
@@ -2488,11 +2510,11 @@
         <v>2</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2550,7 +2572,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -2594,7 +2616,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
@@ -2619,7 +2641,7 @@
       </c>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -2627,7 +2649,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>20</v>
@@ -2679,7 +2701,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>25</v>
@@ -2698,7 +2720,7 @@
       </c>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -2706,7 +2728,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>20</v>
@@ -2725,21 +2747,21 @@
       </c>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A11" s="7">
         <v>2018</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>6</v>
@@ -2810,7 +2832,7 @@
         <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>38</v>
@@ -2866,7 +2888,7 @@
         <v>13</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>7</v>
@@ -2884,16 +2906,16 @@
         <v>2002</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>6</v>
@@ -2906,19 +2928,19 @@
       </c>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A18" s="7">
         <v>2002</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>6</v>
@@ -2936,7 +2958,7 @@
         <v>2002</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
@@ -2961,14 +2983,14 @@
         <v>2003</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>6</v>
@@ -2981,19 +3003,19 @@
       </c>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A21" s="7">
         <v>2003</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>6</v>
@@ -3006,21 +3028,21 @@
       </c>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A22" s="7">
         <v>2003</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>6</v>
@@ -3033,21 +3055,21 @@
       </c>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A23" s="7">
         <v>2003</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>6</v>
@@ -3060,12 +3082,12 @@
       </c>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A24" s="7">
         <v>2004</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
@@ -3090,14 +3112,14 @@
         <v>2004</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>6</v>
@@ -3115,16 +3137,16 @@
         <v>2004</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>6</v>
@@ -3137,12 +3159,12 @@
       </c>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A27" s="7">
         <v>2004</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
@@ -3162,21 +3184,21 @@
       </c>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A28" s="7">
         <v>2004</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>6</v>
@@ -3194,14 +3216,14 @@
         <v>2004</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>7</v>
@@ -3214,12 +3236,12 @@
       </c>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" s="7">
         <v>2005</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
@@ -3247,7 +3269,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -3266,19 +3288,19 @@
       </c>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A32" s="7">
         <v>2019</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>6</v>
@@ -3296,7 +3318,7 @@
         <v>2006</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
@@ -3321,7 +3343,7 @@
         <v>2006</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
@@ -3346,7 +3368,7 @@
         <v>2006</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>419</v>
@@ -3355,7 +3377,7 @@
         <v>38</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>6</v>
@@ -3373,16 +3395,16 @@
         <v>2019</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>6</v>
@@ -3400,14 +3422,14 @@
         <v>2006</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>6</v>
@@ -3425,14 +3447,14 @@
         <v>2007</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>7</v>
@@ -3450,16 +3472,16 @@
         <v>2007</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>6</v>
@@ -3477,7 +3499,7 @@
         <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>423</v>
@@ -3486,7 +3508,7 @@
         <v>30</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>6</v>
@@ -3504,14 +3526,14 @@
         <v>2007</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>6</v>
@@ -3529,7 +3551,7 @@
         <v>2008</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
@@ -3554,14 +3576,14 @@
         <v>2008</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>6</v>
@@ -3579,16 +3601,16 @@
         <v>2009</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>6</v>
@@ -3601,19 +3623,19 @@
       </c>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A45" s="7">
         <v>2009</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>6</v>
@@ -3626,19 +3648,19 @@
       </c>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A46" s="7">
         <v>2019</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>6</v>
@@ -3656,14 +3678,14 @@
         <v>2009</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>7</v>
@@ -3681,14 +3703,14 @@
         <v>2009</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>6</v>
@@ -3706,14 +3728,14 @@
         <v>2010</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>7</v>
@@ -3731,14 +3753,14 @@
         <v>2010</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>7</v>
@@ -3756,14 +3778,14 @@
         <v>2010</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>7</v>
@@ -3781,14 +3803,14 @@
         <v>2011</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>6</v>
@@ -3806,14 +3828,14 @@
         <v>2011</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>7</v>
@@ -3826,21 +3848,21 @@
       </c>
       <c r="I53" s="7"/>
     </row>
-    <row r="54" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A54" s="7">
         <v>2011</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>6</v>
@@ -3853,21 +3875,21 @@
       </c>
       <c r="I54" s="7"/>
     </row>
-    <row r="55" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A55" s="7">
         <v>2020</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>427</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>6</v>
@@ -3880,19 +3902,19 @@
       </c>
       <c r="I55" s="7"/>
     </row>
-    <row r="56" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="7">
         <v>2011</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>6</v>
@@ -3905,19 +3927,19 @@
       </c>
       <c r="I56" s="7"/>
     </row>
-    <row r="57" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A57" s="7">
         <v>2011</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>7</v>
@@ -3930,19 +3952,19 @@
       </c>
       <c r="I57" s="7"/>
     </row>
-    <row r="58" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A58" s="7">
         <v>2011</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>6</v>
@@ -3960,16 +3982,16 @@
         <v>2019</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>426</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>6</v>
@@ -3982,21 +4004,21 @@
       </c>
       <c r="I59" s="7"/>
     </row>
-    <row r="60" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A60" s="7">
         <v>2011</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>6</v>
@@ -4014,14 +4036,14 @@
         <v>2012</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>6</v>
@@ -4039,14 +4061,14 @@
         <v>2012</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>6</v>
@@ -4064,14 +4086,14 @@
         <v>2021</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>6</v>
@@ -4089,17 +4111,17 @@
         <v>2023</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="F64" s="7" t="s">
         <v>6</v>
       </c>
@@ -4111,19 +4133,19 @@
       </c>
       <c r="I64" s="7"/>
     </row>
-    <row r="65" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A65" s="7">
         <v>2012</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>6</v>
@@ -4141,14 +4163,14 @@
         <v>2012</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>6</v>
@@ -4161,19 +4183,19 @@
       </c>
       <c r="I66" s="7"/>
     </row>
-    <row r="67" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A67" s="7">
         <v>2012</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>6</v>
@@ -4191,16 +4213,16 @@
         <v>2012</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>6</v>
@@ -4218,16 +4240,16 @@
         <v>2006</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>6</v>
@@ -4245,14 +4267,14 @@
         <v>2005</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>6</v>
@@ -4270,14 +4292,14 @@
         <v>2012</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>6</v>
@@ -4290,21 +4312,21 @@
       </c>
       <c r="I71" s="7"/>
     </row>
-    <row r="72" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A72" s="7">
         <v>2013</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>6</v>
@@ -4322,16 +4344,16 @@
         <v>2013</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>6</v>
@@ -4344,21 +4366,21 @@
       </c>
       <c r="I73" s="7"/>
     </row>
-    <row r="74" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A74" s="7">
         <v>2013</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>6</v>
@@ -4371,21 +4393,21 @@
       </c>
       <c r="I74" s="7"/>
     </row>
-    <row r="75" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A75" s="7">
         <v>2013</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>6</v>
@@ -4398,19 +4420,19 @@
       </c>
       <c r="I75" s="7"/>
     </row>
-    <row r="76" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A76" s="7">
         <v>2013</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>6</v>
@@ -4428,14 +4450,14 @@
         <v>2013</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>7</v>
@@ -4453,14 +4475,14 @@
         <v>2013</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>7</v>
@@ -4473,21 +4495,21 @@
       </c>
       <c r="I78" s="7"/>
     </row>
-    <row r="79" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A79" s="7">
         <v>2013</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>6</v>
@@ -4505,14 +4527,14 @@
         <v>2014</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>6</v>
@@ -4530,16 +4552,16 @@
         <v>2014</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>6</v>
@@ -4552,21 +4574,21 @@
       </c>
       <c r="I81" s="7"/>
     </row>
-    <row r="82" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A82" s="7">
         <v>2014</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>6</v>
@@ -4584,16 +4606,16 @@
         <v>2014</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>6</v>
@@ -4611,14 +4633,14 @@
         <v>2014</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>6</v>
@@ -4636,14 +4658,14 @@
         <v>2014</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>6</v>
@@ -4661,14 +4683,14 @@
         <v>2014</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>7</v>
@@ -4681,21 +4703,21 @@
       </c>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A87" s="7">
         <v>2014</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>6</v>
@@ -4713,16 +4735,16 @@
         <v>2014</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>6</v>
@@ -4740,16 +4762,16 @@
         <v>2014</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>6</v>
@@ -4767,14 +4789,14 @@
         <v>2014</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>6</v>
@@ -4787,19 +4809,19 @@
       </c>
       <c r="I90" s="7"/>
     </row>
-    <row r="91" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A91" s="7">
         <v>2014</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>7</v>
@@ -4812,21 +4834,21 @@
       </c>
       <c r="I91" s="7"/>
     </row>
-    <row r="92" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A92" s="7">
         <v>2015</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>6</v>
@@ -4844,16 +4866,16 @@
         <v>2015</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>6</v>
@@ -4866,19 +4888,19 @@
       </c>
       <c r="I93" s="7"/>
     </row>
-    <row r="94" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A94" s="7">
         <v>2015</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>6</v>
@@ -4896,14 +4918,14 @@
         <v>2015</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>6</v>
@@ -4916,19 +4938,19 @@
       </c>
       <c r="I95" s="7"/>
     </row>
-    <row r="96" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A96" s="7">
         <v>2015</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>6</v>
@@ -4946,16 +4968,16 @@
         <v>2015</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F97" s="7" t="s">
         <v>6</v>
@@ -4968,19 +4990,19 @@
       </c>
       <c r="I97" s="7"/>
     </row>
-    <row r="98" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A98" s="7">
         <v>2015</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>6</v>
@@ -4998,14 +5020,14 @@
         <v>2021</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>6</v>
@@ -5023,14 +5045,14 @@
         <v>2015</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>6</v>
@@ -5048,16 +5070,16 @@
         <v>2015</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>421</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>6</v>
@@ -5070,21 +5092,21 @@
       </c>
       <c r="I101" s="7"/>
     </row>
-    <row r="102" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:9" s="5" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="7">
         <v>2015</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>6</v>
@@ -5102,14 +5124,14 @@
         <v>2015</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>6</v>
@@ -5127,14 +5149,14 @@
         <v>2015</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>6</v>
@@ -5152,14 +5174,14 @@
         <v>2015</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>7</v>
@@ -5177,7 +5199,7 @@
         <v>2015</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
@@ -5197,19 +5219,19 @@
       </c>
       <c r="I106" s="7"/>
     </row>
-    <row r="107" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A107" s="7">
         <v>2015</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>7</v>
@@ -5222,21 +5244,21 @@
       </c>
       <c r="I107" s="7"/>
     </row>
-    <row r="108" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A108" s="7">
         <v>2016</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>6</v>
@@ -5254,14 +5276,14 @@
         <v>2016</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>6</v>
@@ -5279,16 +5301,16 @@
         <v>2016</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>422</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>6</v>
@@ -5306,14 +5328,14 @@
         <v>2016</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>6</v>
@@ -5326,21 +5348,21 @@
       </c>
       <c r="I111" s="7"/>
     </row>
-    <row r="112" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A112" s="7">
         <v>2017</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>6</v>
@@ -5353,19 +5375,19 @@
       </c>
       <c r="I112" s="7"/>
     </row>
-    <row r="113" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A113" s="7">
         <v>2017</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>6</v>
@@ -5378,19 +5400,19 @@
       </c>
       <c r="I113" s="7"/>
     </row>
-    <row r="114" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A114" s="7">
         <v>2017</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>6</v>
@@ -5408,14 +5430,14 @@
         <v>2017</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>6</v>
@@ -5428,21 +5450,21 @@
       </c>
       <c r="I115" s="7"/>
     </row>
-    <row r="116" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A116" s="7">
         <v>2017</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>6</v>
@@ -5460,14 +5482,14 @@
         <v>2017</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>6</v>
@@ -5480,19 +5502,19 @@
       </c>
       <c r="I117" s="7"/>
     </row>
-    <row r="118" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A118" s="7">
         <v>2017</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>7</v>
@@ -5505,21 +5527,21 @@
       </c>
       <c r="I118" s="7"/>
     </row>
-    <row r="119" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A119" s="7">
         <v>2017</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>6</v>
@@ -5537,16 +5559,16 @@
         <v>2017</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>6</v>
@@ -5559,21 +5581,21 @@
       </c>
       <c r="I120" s="7"/>
     </row>
-    <row r="121" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A121" s="7">
         <v>2017</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>6</v>
@@ -5591,7 +5613,7 @@
         <v>2011</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>420</v>
@@ -5600,7 +5622,7 @@
         <v>30</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>6</v>
@@ -5613,21 +5635,21 @@
       </c>
       <c r="I122" s="7"/>
     </row>
-    <row r="123" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A123" s="7">
         <v>2017</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>6</v>
@@ -5645,16 +5667,16 @@
         <v>2017</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>422</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>6</v>
@@ -5667,21 +5689,21 @@
       </c>
       <c r="I124" s="7"/>
     </row>
-    <row r="125" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A125" s="7">
         <v>2017</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>6</v>
@@ -5699,14 +5721,14 @@
         <v>2017</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>6</v>
@@ -5724,14 +5746,14 @@
         <v>2018</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>6</v>
@@ -5749,16 +5771,16 @@
         <v>2018</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>6</v>
@@ -5776,14 +5798,14 @@
         <v>2018</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>103</v>
+        <v>430</v>
       </c>
       <c r="F129" s="7" t="s">
         <v>7</v>
@@ -5796,21 +5818,21 @@
       </c>
       <c r="I129" s="7"/>
     </row>
-    <row r="130" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A130" s="7">
         <v>2018</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F130" s="7" t="s">
         <v>6</v>
@@ -5823,21 +5845,21 @@
       </c>
       <c r="I130" s="7"/>
     </row>
-    <row r="131" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A131" s="7">
         <v>2018</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F131" s="7" t="s">
         <v>6</v>
@@ -5855,14 +5877,14 @@
         <v>2018</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F132" s="7" t="s">
         <v>6</v>
@@ -5875,19 +5897,19 @@
       </c>
       <c r="I132" s="7"/>
     </row>
-    <row r="133" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A133" s="7">
         <v>2011</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>6</v>
@@ -5905,14 +5927,14 @@
         <v>2018</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F134" s="7" t="s">
         <v>6</v>
@@ -5930,14 +5952,14 @@
         <v>2018</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F135" s="7" t="s">
         <v>7</v>
@@ -5955,16 +5977,16 @@
         <v>2018</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>6</v>
@@ -5977,21 +5999,21 @@
       </c>
       <c r="I136" s="7"/>
     </row>
-    <row r="137" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A137" s="7">
         <v>2018</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>424</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F137" s="7" t="s">
         <v>6</v>
@@ -6004,19 +6026,19 @@
       </c>
       <c r="I137" s="7"/>
     </row>
-    <row r="138" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A138" s="7">
         <v>2012</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F138" s="7" t="s">
         <v>6</v>
@@ -6034,16 +6056,16 @@
         <v>2018</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>25</v>
+        <v>403</v>
+      </c>
+      <c r="D139" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F139" s="7" t="s">
         <v>6</v>
@@ -6056,19 +6078,19 @@
       </c>
       <c r="I139" s="7"/>
     </row>
-    <row r="140" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A140" s="7">
         <v>2018</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F140" s="7" t="s">
         <v>7</v>
@@ -6081,19 +6103,19 @@
       </c>
       <c r="I140" s="7"/>
     </row>
-    <row r="141" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A141" s="7">
         <v>2018</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F141" s="7" t="s">
         <v>6</v>
@@ -6106,19 +6128,19 @@
       </c>
       <c r="I141" s="7"/>
     </row>
-    <row r="142" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A142" s="7">
         <v>2018</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F142" s="7" t="s">
         <v>6</v>
@@ -6136,16 +6158,16 @@
         <v>2018</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>425</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F143" s="7" t="s">
         <v>6</v>
@@ -6163,16 +6185,16 @@
         <v>2019</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F144" s="7" t="s">
         <v>6</v>
@@ -6190,14 +6212,14 @@
         <v>2019</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F145" s="7" t="s">
         <v>6</v>
@@ -6210,19 +6232,19 @@
       </c>
       <c r="I145" s="7"/>
     </row>
-    <row r="146" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A146" s="7">
         <v>2019</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F146" s="7" t="s">
         <v>6</v>
@@ -6240,14 +6262,14 @@
         <v>2015</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F147" s="7" t="s">
         <v>6</v>
@@ -6265,16 +6287,16 @@
         <v>2006</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F148" s="7" t="s">
         <v>6</v>
@@ -6287,21 +6309,21 @@
       </c>
       <c r="I148" s="7"/>
     </row>
-    <row r="149" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A149" s="7">
         <v>2012</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F149" s="7" t="s">
         <v>6</v>
@@ -6319,16 +6341,16 @@
         <v>2007</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F150" s="7" t="s">
         <v>6</v>
@@ -6341,19 +6363,19 @@
       </c>
       <c r="I150" s="7"/>
     </row>
-    <row r="151" spans="1:9" s="5" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A151" s="7">
         <v>2019</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F151" s="7" t="s">
         <v>6</v>
@@ -6371,14 +6393,14 @@
         <v>2019</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F152" s="7" t="s">
         <v>6</v>
@@ -6396,16 +6418,16 @@
         <v>2019</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F153" s="7" t="s">
         <v>6</v>
@@ -6418,19 +6440,19 @@
       </c>
       <c r="I153" s="7"/>
     </row>
-    <row r="154" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A154" s="7">
         <v>2019</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F154" s="7" t="s">
         <v>6</v>
@@ -6448,16 +6470,16 @@
         <v>2020</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F155" s="7" t="s">
         <v>6</v>
@@ -6475,16 +6497,16 @@
         <v>2012</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>558</v>
+        <v>436</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F156" s="7" t="s">
         <v>6</v>
@@ -6502,14 +6524,14 @@
         <v>2020</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F157" s="7" t="s">
         <v>6</v>
@@ -6527,14 +6549,14 @@
         <v>2020</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F158" s="7" t="s">
         <v>6</v>
@@ -6552,16 +6574,16 @@
         <v>2020</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F159" s="7" t="s">
         <v>6</v>
@@ -6579,14 +6601,14 @@
         <v>2020</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F160" s="7" t="s">
         <v>7</v>
@@ -6604,16 +6626,16 @@
         <v>2020</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F161" s="7" t="s">
         <v>6</v>
@@ -6631,14 +6653,14 @@
         <v>2020</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F162" s="7" t="s">
         <v>6</v>
@@ -6656,7 +6678,7 @@
         <v>2020</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
@@ -6681,10 +6703,10 @@
         <v>2020</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>38</v>
@@ -6708,14 +6730,14 @@
         <v>2020</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F165" s="7" t="s">
         <v>6</v>
@@ -6733,16 +6755,16 @@
         <v>2020</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>417</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F166" s="7" t="s">
         <v>6</v>
@@ -6760,16 +6782,16 @@
         <v>2020</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F167" s="7" t="s">
         <v>6</v>
@@ -6787,14 +6809,14 @@
         <v>2020</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F168" s="7" t="s">
         <v>6</v>
@@ -6812,16 +6834,16 @@
         <v>2020</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F169" s="7" t="s">
         <v>6</v>
@@ -6839,16 +6861,16 @@
         <v>2020</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F170" s="7" t="s">
         <v>6</v>
@@ -6866,16 +6888,16 @@
         <v>2020</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F171" s="7" t="s">
         <v>6</v>
@@ -6893,16 +6915,16 @@
         <v>2020</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F172" s="7" t="s">
         <v>6</v>
@@ -6920,14 +6942,14 @@
         <v>2020</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F173" s="7" t="s">
         <v>6</v>
@@ -6945,16 +6967,16 @@
         <v>2020</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>418</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F174" s="7" t="s">
         <v>6</v>
@@ -6972,16 +6994,16 @@
         <v>2020</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F175" s="7" t="s">
         <v>6</v>
@@ -6999,16 +7021,16 @@
         <v>2021</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F176" s="7" t="s">
         <v>6</v>
@@ -7026,16 +7048,16 @@
         <v>2021</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>558</v>
+        <v>442</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F177" s="7" t="s">
         <v>6</v>
@@ -7053,16 +7075,16 @@
         <v>2021</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F178" s="7" t="s">
         <v>6</v>
@@ -7080,16 +7102,16 @@
         <v>2021</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>428</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F179" s="7" t="s">
         <v>6</v>
@@ -7107,14 +7129,14 @@
         <v>2021</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F180" s="7" t="s">
         <v>6</v>
@@ -7132,16 +7154,16 @@
         <v>2021</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F181" s="7" t="s">
         <v>6</v>
@@ -7159,14 +7181,14 @@
         <v>2021</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F182" s="7" t="s">
         <v>6</v>
@@ -7184,14 +7206,14 @@
         <v>2021</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F183" s="7" t="s">
         <v>6</v>
@@ -7209,7 +7231,7 @@
         <v>2021</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
@@ -7234,16 +7256,16 @@
         <v>2021</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F185" s="7" t="s">
         <v>6</v>
@@ -7261,14 +7283,14 @@
         <v>2021</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F186" s="7" t="s">
         <v>6</v>
@@ -7286,16 +7308,16 @@
         <v>2021</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F187" s="7" t="s">
         <v>6</v>
@@ -7313,16 +7335,16 @@
         <v>2021</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F188" s="7" t="s">
         <v>6</v>
@@ -7340,14 +7362,14 @@
         <v>2021</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F189" s="7" t="s">
         <v>6</v>
@@ -7365,16 +7387,16 @@
         <v>2012</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F190" s="7" t="s">
         <v>6</v>
@@ -7392,16 +7414,16 @@
         <v>2021</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F191" s="7" t="s">
         <v>6</v>
@@ -7419,16 +7441,16 @@
         <v>2018</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>423</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F192" s="7" t="s">
         <v>6</v>
@@ -7446,16 +7468,16 @@
         <v>2022</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F193" s="7" t="s">
         <v>6</v>
@@ -7473,14 +7495,14 @@
         <v>2022</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F194" s="7" t="s">
         <v>6</v>
@@ -7498,16 +7520,16 @@
         <v>2022</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F195" s="7" t="s">
         <v>6</v>
@@ -7525,16 +7547,16 @@
         <v>2022</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="F196" s="7" t="s">
         <v>6</v>
@@ -7552,14 +7574,14 @@
         <v>2022</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F197" s="7" t="s">
         <v>6</v>
@@ -7577,14 +7599,14 @@
         <v>2022</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="F198" s="7" t="s">
         <v>6</v>
@@ -7602,14 +7624,14 @@
         <v>2022</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F199" s="7" t="s">
         <v>6</v>
@@ -7627,16 +7649,16 @@
         <v>2022</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F200" s="7" t="s">
         <v>6</v>
@@ -7649,21 +7671,21 @@
       </c>
       <c r="I200" s="7"/>
     </row>
-    <row r="201" spans="1:9" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A201" s="7">
         <v>2022</v>
       </c>
-      <c r="B201" s="2" t="s">
-        <v>348</v>
+      <c r="B201" s="16" t="s">
+        <v>561</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>349</v>
+        <v>154</v>
+      </c>
+      <c r="E201" s="16" t="s">
+        <v>562</v>
       </c>
       <c r="F201" s="7" t="s">
         <v>6</v>
@@ -7681,16 +7703,16 @@
         <v>2022</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E202" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="F202" s="7" t="s">
         <v>6</v>
@@ -7708,14 +7730,14 @@
         <v>2022</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F203" s="7" t="s">
         <v>6</v>
@@ -7733,14 +7755,14 @@
         <v>2022</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>6</v>
@@ -7758,16 +7780,16 @@
         <v>2023</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E205" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>6</v>
@@ -7785,16 +7807,16 @@
         <v>2023</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>557</v>
+        <v>416</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F206" s="7" t="s">
         <v>6</v>
@@ -7812,14 +7834,14 @@
         <v>2023</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F207" s="7" t="s">
         <v>6</v>
@@ -7837,14 +7859,14 @@
         <v>2023</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="F208" s="7" t="s">
         <v>6</v>
@@ -7862,14 +7884,14 @@
         <v>2023</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F209" s="7" t="s">
         <v>6</v>
@@ -7887,14 +7909,14 @@
         <v>2023</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F210" s="7" t="s">
         <v>6</v>
@@ -7912,14 +7934,14 @@
         <v>2023</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F211" s="7" t="s">
         <v>6</v>
@@ -7937,14 +7959,14 @@
         <v>2023</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F212" s="7" t="s">
         <v>6</v>
@@ -7962,16 +7984,16 @@
         <v>2023</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="F213" s="7" t="s">
         <v>6</v>
@@ -7989,14 +8011,14 @@
         <v>2009</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F214" s="7" t="s">
         <v>6</v>
@@ -8014,14 +8036,14 @@
         <v>2023</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F215" s="7" t="s">
         <v>6</v>
@@ -8039,14 +8061,14 @@
         <v>2023</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F216" s="7" t="s">
         <v>6</v>
@@ -8064,14 +8086,14 @@
         <v>2023</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F217" s="7" t="s">
         <v>6</v>
@@ -8089,14 +8111,14 @@
         <v>2023</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F218" s="7" t="s">
         <v>6</v>
@@ -8114,13 +8136,13 @@
         <v>2024</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F219" s="7" t="s">
         <v>6</v>
@@ -8137,14 +8159,14 @@
         <v>2024</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C220" s="13"/>
       <c r="D220" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F220" s="7" t="s">
         <v>6</v>
@@ -8161,16 +8183,16 @@
         <v>2024</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E221" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="F221" s="7" t="s">
         <v>6</v>
@@ -8187,14 +8209,14 @@
         <v>2024</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F222" s="7" t="s">
         <v>6</v>
@@ -8211,14 +8233,14 @@
         <v>2024</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F223" s="7" t="s">
         <v>6</v>
@@ -8235,16 +8257,16 @@
         <v>2024</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>6</v>
@@ -8261,16 +8283,16 @@
         <v>2024</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C225" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E225" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>6</v>
@@ -8287,16 +8309,16 @@
         <v>2024</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F226" s="7" t="s">
         <v>6</v>
@@ -8314,16 +8336,16 @@
         <v>2024</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F227" s="7" t="s">
         <v>6</v>
@@ -8340,16 +8362,16 @@
         <v>2024</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F228" s="7" t="s">
         <v>6</v>
@@ -8366,16 +8388,16 @@
         <v>2024</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F229" s="7" t="s">
         <v>6</v>
@@ -8392,14 +8414,14 @@
         <v>2024</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F230" s="7" t="s">
         <v>6</v>
@@ -8416,16 +8438,16 @@
         <v>2024</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F231" s="7" t="s">
         <v>6</v>
@@ -8442,10 +8464,10 @@
         <v>2024</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>38</v>
@@ -8468,16 +8490,16 @@
         <v>2024</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D233" s="14" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E233" s="14" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F233" s="7" t="s">
         <v>6</v>
@@ -8494,13 +8516,13 @@
         <v>2024</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F234" s="7" t="s">
         <v>6</v>
@@ -8517,16 +8539,16 @@
         <v>2024</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F235" s="7" t="s">
         <v>6</v>
@@ -8543,16 +8565,16 @@
         <v>2025</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F236" s="7" t="s">
         <v>6</v>
@@ -8569,16 +8591,16 @@
         <v>2025</v>
       </c>
       <c r="B237" s="14" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C237" s="14" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D237" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E237" s="14" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F237" s="5" t="s">
         <v>6</v>
@@ -8595,16 +8617,16 @@
         <v>2025</v>
       </c>
       <c r="B238" s="14" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D238" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E238" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F238" s="5" t="s">
         <v>6</v>
@@ -8621,14 +8643,14 @@
         <v>2025</v>
       </c>
       <c r="B239" s="14" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C239" s="12"/>
       <c r="D239" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E239" s="14" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>6</v>
@@ -8645,14 +8667,14 @@
         <v>2025</v>
       </c>
       <c r="B240" s="14" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C240" s="12"/>
       <c r="D240" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E240" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F240" s="5" t="s">
         <v>6</v>
@@ -8669,16 +8691,16 @@
         <v>2025</v>
       </c>
       <c r="B241" s="14" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C241" s="14" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D241" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E241" s="14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F241" s="5" t="s">
         <v>6</v>
@@ -8695,16 +8717,16 @@
         <v>2025</v>
       </c>
       <c r="B242" s="14" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D242" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E242" s="14" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F242" s="5" t="s">
         <v>6</v>
@@ -8721,16 +8743,16 @@
         <v>2025</v>
       </c>
       <c r="B243" s="14" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C243" s="14" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D243" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E243" s="14" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F243" s="5" t="s">
         <v>6</v>
@@ -8747,14 +8769,14 @@
         <v>2025</v>
       </c>
       <c r="B244" s="14" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C244" s="14"/>
       <c r="D244" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E244" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F244" s="5" t="s">
         <v>6</v>
@@ -8766,21 +8788,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="245" spans="1:9" s="5" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:9" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A245" s="5">
         <v>2025</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D245" s="14" t="s">
-        <v>53</v>
+        <v>387</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F245" s="5" t="s">
         <v>6</v>
@@ -8797,16 +8819,16 @@
         <v>2025</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="D246" s="14" t="s">
-        <v>530</v>
+        <v>533</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>532</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F246" s="5" t="s">
         <v>6</v>
@@ -8819,21 +8841,21 @@
       </c>
       <c r="I246" s="6"/>
     </row>
-    <row r="247" spans="1:9" s="15" customFormat="1" ht="29" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A247" s="5">
         <v>2025</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="D247" s="14" t="s">
-        <v>53</v>
+        <v>536</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>6</v>
@@ -8850,16 +8872,16 @@
         <v>2025</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D248" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D248" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F248" s="7" t="s">
         <v>6</v>
@@ -8876,16 +8898,16 @@
         <v>2025</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>6</v>
@@ -8897,21 +8919,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" spans="1:9" s="7" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:9" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.15">
       <c r="A250" s="7">
         <v>2025</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>53</v>
+        <v>544</v>
+      </c>
+      <c r="C250" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="D250" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>6</v>
@@ -8928,16 +8950,16 @@
         <v>2025</v>
       </c>
       <c r="B251" s="14" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C251" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D251" s="14" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="E251" s="14" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>6</v>
@@ -8949,106 +8971,353 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:9" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.2">
-      <c r="A252" s="4">
+    <row r="252" spans="1:9" s="5" customFormat="1" ht="70" x14ac:dyDescent="0.15">
+      <c r="A252" s="16">
         <v>2026</v>
       </c>
       <c r="B252" s="16" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="C252" s="16"/>
       <c r="D252" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="E252" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G252" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H252" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="43" x14ac:dyDescent="0.2">
+      <c r="A253" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B253" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="C253" s="14"/>
+      <c r="D253" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="E253" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="F253" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G253" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H253" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I253" s="6"/>
+    </row>
+    <row r="254" spans="1:9" ht="29" x14ac:dyDescent="0.2">
+      <c r="A254" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B254" s="14" t="s">
         <v>551</v>
       </c>
-      <c r="E252" s="16" t="s">
+      <c r="C254" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="D254" s="14" t="s">
         <v>552</v>
       </c>
-      <c r="F252" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G252" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="H252" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" s="9" customFormat="1" ht="57" x14ac:dyDescent="0.2">
-      <c r="A253" s="4">
+      <c r="E254" s="14" t="s">
+        <v>557</v>
+      </c>
+      <c r="F254" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G254" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H254" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I254" s="6"/>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A255" s="5">
         <v>2026</v>
       </c>
-      <c r="B253" s="16" t="s">
-        <v>545</v>
-      </c>
-      <c r="C253" s="16" t="s">
+      <c r="B255" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="C255" s="14"/>
+      <c r="D255" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E255" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="F255" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G255" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H255" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I255" s="6"/>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A256" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B256" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="D253" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="E253" s="16" t="s">
-        <v>549</v>
-      </c>
-      <c r="F253" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G253" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="H253" s="16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="4">
+      <c r="C256" s="14"/>
+      <c r="D256" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E256" s="14" t="s">
+        <v>556</v>
+      </c>
+      <c r="F256" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G256" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H256" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I256" s="6"/>
+    </row>
+    <row r="257" spans="1:11" ht="43" x14ac:dyDescent="0.2">
+      <c r="A257" s="16">
         <v>2026</v>
       </c>
-      <c r="B254" s="16" t="s">
-        <v>547</v>
-      </c>
-      <c r="C254" s="16"/>
-      <c r="D254" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E254" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="F254" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G254" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="H254" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="4">
+      <c r="B257" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="C257" s="16"/>
+      <c r="D257" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="E257" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="F257" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G257" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H257" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="I257" s="6"/>
+    </row>
+    <row r="258" spans="1:11" ht="43" x14ac:dyDescent="0.2">
+      <c r="A258" s="4">
         <v>2026</v>
       </c>
-      <c r="B255" s="16" t="s">
-        <v>548</v>
-      </c>
-      <c r="C255" s="16"/>
-      <c r="D255" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E255" s="16" t="s">
-        <v>556</v>
-      </c>
-      <c r="F255" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G255" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="H255" s="16" t="s">
-        <v>8</v>
-      </c>
+      <c r="B258" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C258" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="D258" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="E258" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G258" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H258" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I258" s="6"/>
+    </row>
+    <row r="259" spans="1:11" ht="43" x14ac:dyDescent="0.2">
+      <c r="A259" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B259" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="C259" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="D259" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="E259" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G259" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H259" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I259" s="6"/>
+    </row>
+    <row r="260" spans="1:11" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+      <c r="A260" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B260" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="C260" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="D260" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="E260" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G260" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H260" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" s="4" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+      <c r="A261" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B261" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="C261" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="D261" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E261" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="F261" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G261" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H261" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A262" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C262" s="16"/>
+      <c r="D262" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E262" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G262" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H262" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" ht="71" x14ac:dyDescent="0.2">
+      <c r="A263" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C263" s="4"/>
+      <c r="D263" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="E263" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G263" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H263" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" ht="43" x14ac:dyDescent="0.2">
+      <c r="A264" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B264" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="C264" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="D264" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="E264" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="F264" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G264" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H264" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I264" s="16"/>
+      <c r="J264" s="16"/>
+      <c r="K264" s="16"/>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B265"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
+      <c r="E265" s="2"/>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B266"/>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B267"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I255" xr:uid="{6B89377A-76F6-CA40-8081-AAD80BFAB6B8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H217">
     <sortCondition ref="B2:B217"/>
   </sortState>
@@ -9067,37 +9336,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="59" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
